--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,170 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45200</v>
+      </c>
+      <c r="F7" s="2">
         <v>45109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44836</v>
       </c>
-      <c r="H7" s="2">
-        <v>44563</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
+        <v>44745</v>
+      </c>
+      <c r="K7" s="2">
         <v>44472</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3666000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3915000</v>
+      </c>
+      <c r="F8" s="3">
         <v>7863000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3852000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>3767000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>3789000</v>
       </c>
-      <c r="H8" s="3">
-        <v>3733000</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
+        <v>3804000</v>
+      </c>
+      <c r="K8" s="3">
         <v>11321000</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3525000</v>
+        <v>1568000</v>
       </c>
       <c r="E9" s="3">
+        <v>1665000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3513000</v>
+      </c>
+      <c r="G9" s="3">
         <v>1727000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1693000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1675000</v>
-      </c>
       <c r="H9" s="3">
-        <v>1736000</v>
+        <v>1700000</v>
       </c>
       <c r="I9" s="3">
+        <v>1637000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1646000</v>
+      </c>
+      <c r="K9" s="3">
         <v>4851000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4338000</v>
+        <v>2098000</v>
       </c>
       <c r="E10" s="3">
+        <v>2250000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4350000</v>
+      </c>
+      <c r="G10" s="3">
         <v>2125000</v>
       </c>
-      <c r="F10" s="3">
-        <v>2074000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2114000</v>
-      </c>
       <c r="H10" s="3">
-        <v>1997000</v>
+        <v>2067000</v>
       </c>
       <c r="I10" s="3">
+        <v>2152000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2158000</v>
+      </c>
+      <c r="K10" s="3">
         <v>6470000</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,43 +858,51 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>99000</v>
+        <v>133000</v>
       </c>
       <c r="E12" s="3">
+        <v>78000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>188000</v>
+      </c>
+      <c r="G12" s="3">
         <v>89000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>103000</v>
       </c>
-      <c r="G12" s="3">
-        <v>272000</v>
-      </c>
-      <c r="H12" s="3">
-        <v>102000</v>
-      </c>
       <c r="I12" s="3">
+        <v>90000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>94000</v>
+      </c>
+      <c r="K12" s="3">
         <v>253000</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -903,43 +936,55 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>198000</v>
+        <v>251000</v>
       </c>
       <c r="E14" s="3">
+        <v>135000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>212000</v>
+      </c>
+      <c r="G14" s="3">
         <v>15000</v>
       </c>
-      <c r="F14" s="3">
-        <v>11000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>83000</v>
-      </c>
       <c r="H14" s="3">
-        <v>4000</v>
+        <v>22000</v>
       </c>
       <c r="I14" s="3">
+        <v>63000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="K14" s="3">
         <v>102000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -973,8 +1018,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -985,78 +1036,92 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6521000</v>
+        <v>3206000</v>
       </c>
       <c r="E17" s="3">
+        <v>3207000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6533000</v>
+      </c>
+      <c r="G17" s="3">
         <v>3227000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>3236000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3026000</v>
       </c>
-      <c r="H17" s="3">
-        <v>3211000</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>3024000</v>
+      </c>
+      <c r="K17" s="3">
         <v>8898000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1342000</v>
+        <v>460000</v>
       </c>
       <c r="E18" s="3">
+        <v>708000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1330000</v>
+      </c>
+      <c r="G18" s="3">
         <v>625000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>531000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>763000</v>
       </c>
-      <c r="H18" s="3">
-        <v>522000</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>780000</v>
+      </c>
+      <c r="K18" s="3">
         <v>2423000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,92 +1135,106 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-40000</v>
+        <v>11000</v>
       </c>
       <c r="E20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>47000</v>
+      </c>
+      <c r="G20" s="3">
         <v>-16000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-19000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-25000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-15000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1602000</v>
+        <v>645000</v>
       </c>
       <c r="E21" s="3">
+        <v>853000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1677000</v>
+      </c>
+      <c r="G21" s="3">
         <v>761000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>678000</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3">
+        <v>890000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>936000</v>
+      </c>
+      <c r="K21" s="3">
         <v>2957000</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>54000</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+        <v>114000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>115000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>129000</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1163,90 +1242,108 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>357000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>585000</v>
+      </c>
+      <c r="F23" s="3">
         <v>1248000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>609000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>512000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>738000</v>
       </c>
-      <c r="H23" s="3">
-        <v>517000</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>775000</v>
+      </c>
+      <c r="K23" s="3">
         <v>2408000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>147000</v>
+      </c>
+      <c r="F24" s="3">
         <v>349000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>279000</v>
       </c>
-      <c r="F24" s="3">
-        <v>142000</v>
-      </c>
-      <c r="G24" s="3">
-        <v>152000</v>
-      </c>
       <c r="H24" s="3">
-        <v>106000</v>
+        <v>165000</v>
       </c>
       <c r="I24" s="3">
+        <v>153000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>171000</v>
+      </c>
+      <c r="K24" s="3">
         <v>788000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1280,78 +1377,96 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>438000</v>
+      </c>
+      <c r="F26" s="3">
         <v>899000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>330000</v>
       </c>
-      <c r="F26" s="3">
-        <v>370000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>586000</v>
-      </c>
       <c r="H26" s="3">
-        <v>411000</v>
+        <v>347000</v>
       </c>
       <c r="I26" s="3">
+        <v>585000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>604000</v>
+      </c>
+      <c r="K26" s="3">
         <v>1620000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>438000</v>
+      </c>
+      <c r="F27" s="3">
         <v>899000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>330000</v>
       </c>
-      <c r="F27" s="3">
-        <v>370000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>586000</v>
-      </c>
       <c r="H27" s="3">
-        <v>411000</v>
+        <v>347000</v>
       </c>
       <c r="I27" s="3">
+        <v>585000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>604000</v>
+      </c>
+      <c r="K27" s="3">
         <v>1620000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1385,8 +1500,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1420,8 +1541,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1455,8 +1582,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1490,78 +1623,96 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>40000</v>
+        <v>-11000</v>
       </c>
       <c r="E32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="G32" s="3">
         <v>16000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>19000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>25000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>15000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>438000</v>
+      </c>
+      <c r="F33" s="3">
         <v>899000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>330000</v>
       </c>
-      <c r="F33" s="3">
-        <v>370000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>586000</v>
-      </c>
       <c r="H33" s="3">
-        <v>411000</v>
+        <v>347000</v>
       </c>
       <c r="I33" s="3">
+        <v>585000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>604000</v>
+      </c>
+      <c r="K33" s="3">
         <v>1620000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1595,83 +1746,101 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>438000</v>
+      </c>
+      <c r="F35" s="3">
         <v>899000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>330000</v>
       </c>
-      <c r="F35" s="3">
-        <v>370000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>586000</v>
-      </c>
       <c r="H35" s="3">
-        <v>411000</v>
+        <v>347000</v>
       </c>
       <c r="I35" s="3">
+        <v>585000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>604000</v>
+      </c>
+      <c r="K35" s="3">
         <v>1620000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45200</v>
+      </c>
+      <c r="F38" s="2">
         <v>45109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44836</v>
       </c>
-      <c r="H38" s="2">
-        <v>44563</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
+        <v>44745</v>
+      </c>
+      <c r="K38" s="2">
         <v>44472</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1685,8 +1854,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,28 +1871,30 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1231000</v>
+        <v>1382000</v>
       </c>
       <c r="E41" s="3">
-        <v>1691000</v>
+        <v>1062000</v>
       </c>
       <c r="F41" s="3">
         <v>1231000</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+      <c r="G41" s="3">
+        <v>1691000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1231000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>797000</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1735,8 +1908,14 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1770,28 +1949,34 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2096000</v>
+        <v>2073000</v>
       </c>
       <c r="E43" s="3">
         <v>2109000</v>
       </c>
       <c r="F43" s="3">
+        <v>2096000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2109000</v>
+      </c>
+      <c r="H43" s="3">
         <v>2122000</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3">
+        <v>2141000</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
@@ -1805,28 +1990,34 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1851000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1885000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2026000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2222000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2226000</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+      <c r="I44" s="3">
+        <v>2133000</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -1840,28 +2031,34 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>832000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>838000</v>
+      </c>
+      <c r="F45" s="3">
         <v>866000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>417000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>298000</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>392000</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1875,28 +2072,34 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6138000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5894000</v>
+      </c>
+      <c r="F46" s="3">
         <v>6219000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6439000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5877000</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
+      <c r="I46" s="3">
+        <v>5463000</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -1910,8 +2113,14 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1945,28 +2154,34 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2181000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1872000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1832000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1836000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1820000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
+      <c r="I48" s="3">
+        <v>1700000</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
@@ -1980,28 +2195,34 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18890000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>18461000</v>
+      </c>
+      <c r="F49" s="3">
         <v>18759000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>19071000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>19038000</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="I49" s="3">
+        <v>18315000</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
@@ -2015,8 +2236,14 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2050,8 +2277,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2085,28 +2318,34 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>642000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>850000</v>
+      </c>
+      <c r="F52" s="3">
         <v>732000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8249000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>581000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>544000</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2120,8 +2359,14 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2155,28 +2400,34 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27851000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>27077000</v>
+      </c>
+      <c r="F54" s="3">
         <v>27542000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>35595000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27316000</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
+      <c r="I54" s="3">
+        <v>26022000</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2190,8 +2441,14 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2205,8 +2462,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2220,28 +2479,30 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2489000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2281000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2354000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1781000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1829000</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
+      <c r="I57" s="3">
+        <v>1745000</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
@@ -2255,20 +2516,26 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>513000</v>
+      </c>
+      <c r="F58" s="3">
         <v>752000</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,37 +2548,43 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2393000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2367000</v>
+      </c>
+      <c r="F59" s="3">
         <v>2193000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2429000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2097000</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="I59" s="3">
+        <v>2122000</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2325,28 +2598,34 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5481000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5161000</v>
+      </c>
+      <c r="F60" s="3">
         <v>5299000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>4210000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3926000</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
+      <c r="I60" s="3">
+        <v>3867000</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2360,23 +2639,29 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7687000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7685000</v>
+      </c>
+      <c r="F61" s="3">
         <v>7684000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7676000</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2395,28 +2680,34 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3472000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3338000</v>
+      </c>
+      <c r="F62" s="3">
         <v>3519000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3427000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3369000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>3228000</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -2430,8 +2721,14 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2465,8 +2762,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2500,8 +2803,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2535,28 +2844,34 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16640000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16184000</v>
+      </c>
+      <c r="F66" s="3">
         <v>16502000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>15313000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7295000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>7095000</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2570,8 +2885,14 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2585,8 +2906,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2620,8 +2943,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2655,8 +2984,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2690,8 +3025,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2725,28 +3066,34 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>485000</v>
+      </c>
+      <c r="F72" s="3">
         <v>430000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>25521000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>25474000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+      <c r="I72" s="3">
+        <v>25153000</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2760,8 +3107,14 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2795,8 +3148,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2830,8 +3189,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2865,28 +3230,34 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11211000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10893000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11040000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20282000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20021000</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>18927000</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -2900,8 +3271,14 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2935,83 +3312,101 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45200</v>
+      </c>
+      <c r="F80" s="2">
         <v>45109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44836</v>
       </c>
-      <c r="H80" s="2">
-        <v>44563</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
+        <v>44745</v>
+      </c>
+      <c r="K80" s="2">
         <v>44472</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>438000</v>
+      </c>
+      <c r="F81" s="3">
         <v>899000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>330000</v>
       </c>
-      <c r="F81" s="3">
-        <v>370000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>586000</v>
-      </c>
       <c r="H81" s="3">
-        <v>411000</v>
+        <v>347000</v>
       </c>
       <c r="I81" s="3">
+        <v>585000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>604000</v>
+      </c>
+      <c r="K81" s="3">
         <v>1620000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3025,31 +3420,33 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>153000</v>
+      </c>
+      <c r="F83" s="3">
         <v>300000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>152000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>166000</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>152000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>161000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3060,8 +3457,14 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3498,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3130,8 +3539,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3165,8 +3580,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3200,8 +3621,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3235,31 +3662,37 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>950000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>674000</v>
+      </c>
+      <c r="F89" s="3">
         <v>1544000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>802000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>644000</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>736000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>807000</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3270,8 +3703,14 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3285,31 +3724,33 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-223000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-77000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-55000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-159000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-216000</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-103000</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>-76000</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3320,8 +3761,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3355,8 +3802,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3390,31 +3843,37 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-265000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-118000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-41000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-167000</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="I94" s="3">
+        <v>-108000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-73000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3425,8 +3884,14 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3440,13 +3905,15 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-383000</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3475,8 +3942,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3510,8 +3983,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3545,8 +4024,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3580,31 +4065,37 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-383000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-726000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1418000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>7388000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-63000</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="I100" s="3">
+        <v>-635000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-675000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3615,31 +4106,37 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>20000</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-50000</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3650,31 +4147,37 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>320000</v>
       </c>
       <c r="E102" s="3">
+        <v>-169000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>8155000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>434000</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="I102" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>9000</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -3683,6 +4186,12 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,61 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45200</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45109</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45018</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44927</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44836</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44745</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44472</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,38 +721,41 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3894000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3666000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3915000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7863000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3852000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3767000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3789000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3804000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11321000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -761,38 +765,41 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1652000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1568000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1665000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3513000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1727000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1700000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1637000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1646000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4851000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -802,38 +809,41 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2242000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2098000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2250000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4350000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2125000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2067000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2152000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2158000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6470000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,8 +853,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -860,38 +873,39 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E12" s="3">
         <v>133000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>78000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>188000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>89000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>103000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>90000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>94000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>253000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,8 +915,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -942,38 +959,41 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E14" s="3">
         <v>251000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>135000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>212000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>22000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>63000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>102000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -983,8 +1003,11 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1024,8 +1047,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1038,38 +1064,39 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3344000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3206000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3207000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6533000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3227000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3212000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3236000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3026000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3024000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8898000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1079,38 +1106,41 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>550000</v>
+      </c>
+      <c r="E18" s="3">
         <v>460000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>708000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1330000</v>
       </c>
-      <c r="G18" s="3">
-        <v>625000</v>
-      </c>
       <c r="H18" s="3">
+        <v>640000</v>
+      </c>
+      <c r="I18" s="3">
         <v>531000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>763000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>780000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2423000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,8 +1150,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1137,38 +1170,39 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E20" s="3">
         <v>11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>47000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-16000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-25000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1178,38 +1212,41 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>685000</v>
+      </c>
+      <c r="E21" s="3">
         <v>645000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>853000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1677000</v>
       </c>
-      <c r="G21" s="3">
-        <v>761000</v>
-      </c>
       <c r="H21" s="3">
+        <v>772000</v>
+      </c>
+      <c r="I21" s="3">
         <v>678000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>890000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>936000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2957000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,40 +1256,43 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E22" s="3">
         <v>114000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>115000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>129000</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
+      <c r="H22" s="3">
+        <v>11000</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1260,38 +1300,41 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>427000</v>
+      </c>
+      <c r="E23" s="3">
         <v>357000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>585000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1248000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>609000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>512000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>738000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>775000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2408000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,38 +1344,41 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>131000</v>
+      </c>
+      <c r="E24" s="3">
         <v>30000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>147000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>349000</v>
       </c>
-      <c r="G24" s="3">
-        <v>279000</v>
-      </c>
       <c r="H24" s="3">
+        <v>140000</v>
+      </c>
+      <c r="I24" s="3">
         <v>165000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>153000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>171000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>788000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1342,8 +1388,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1383,38 +1432,41 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E26" s="3">
         <v>327000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>438000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>899000</v>
       </c>
-      <c r="G26" s="3">
-        <v>330000</v>
-      </c>
       <c r="H26" s="3">
+        <v>469000</v>
+      </c>
+      <c r="I26" s="3">
         <v>347000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>585000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>604000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1620000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1424,38 +1476,41 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E27" s="3">
         <v>327000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>438000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>899000</v>
       </c>
-      <c r="G27" s="3">
-        <v>330000</v>
-      </c>
       <c r="H27" s="3">
+        <v>469000</v>
+      </c>
+      <c r="I27" s="3">
         <v>347000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>585000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>604000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1620000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1465,8 +1520,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1506,8 +1564,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1547,8 +1608,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1588,8 +1652,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1629,38 +1696,41 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-47000</v>
       </c>
-      <c r="G32" s="3">
-        <v>16000</v>
-      </c>
       <c r="H32" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I32" s="3">
         <v>19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>25000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1670,38 +1740,41 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E33" s="3">
         <v>327000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>438000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>899000</v>
       </c>
-      <c r="G33" s="3">
-        <v>330000</v>
-      </c>
       <c r="H33" s="3">
+        <v>469000</v>
+      </c>
+      <c r="I33" s="3">
         <v>347000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>585000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>604000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1620000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1711,8 +1784,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1752,38 +1828,41 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E35" s="3">
         <v>327000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>438000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>899000</v>
       </c>
-      <c r="G35" s="3">
-        <v>330000</v>
-      </c>
       <c r="H35" s="3">
+        <v>469000</v>
+      </c>
+      <c r="I35" s="3">
         <v>347000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>585000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>604000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1620000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1793,43 +1872,46 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45200</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45109</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45018</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44927</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44836</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44745</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44472</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1839,8 +1921,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1856,8 +1941,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1873,32 +1959,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1155000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1382000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1062000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1231000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1691000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1231000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>797000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1914,8 +2001,11 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1955,32 +2045,35 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2160000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2073000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2109000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2096000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2109000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2122000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2141000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1996,32 +2089,35 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1884000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1851000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1885000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2026000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2222000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2226000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2133000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2037,32 +2133,35 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>898000</v>
+      </c>
+      <c r="E45" s="3">
         <v>832000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>838000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>866000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>417000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>298000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>392000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2078,32 +2177,35 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6097000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6138000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5894000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6219000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6439000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5877000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5463000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2119,8 +2221,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2160,32 +2265,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2145000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2181000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1872000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1832000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1836000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1820000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1700000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2201,32 +2309,35 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18410000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18890000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18461000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18759000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19071000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19038000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18315000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2353,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2283,8 +2397,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2324,32 +2441,35 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>631000</v>
+      </c>
+      <c r="E52" s="3">
         <v>642000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>850000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>732000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8249000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>581000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>544000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2485,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2406,32 +2529,35 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27283000</v>
+      </c>
+      <c r="E54" s="3">
         <v>27851000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27077000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27542000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>35595000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27316000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26022000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2447,8 +2573,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2464,8 +2593,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2481,32 +2611,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2602000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2489000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2281000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2354000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1781000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1829000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1745000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2522,23 +2653,26 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1522000</v>
+      </c>
+      <c r="E58" s="3">
         <v>599000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>513000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>752000</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2554,8 +2688,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2563,32 +2697,35 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2042000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2393000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2367000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2193000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2429000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2097000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2122000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2604,32 +2741,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6166000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5481000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5161000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5299000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4210000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3926000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3867000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,26 +2785,29 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7033000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7687000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7685000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7684000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7676000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2686,32 +2829,35 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3463000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3472000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3338000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3519000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3427000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3369000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3228000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2727,8 +2873,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2768,8 +2917,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2809,8 +2961,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2850,32 +3005,35 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16662000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16640000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16184000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16502000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15313000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7295000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7095000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2891,8 +3049,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2908,8 +3069,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2949,8 +3111,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2990,8 +3155,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3031,8 +3199,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3072,32 +3243,35 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E72" s="3">
         <v>429000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>485000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>430000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25521000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25474000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25153000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3113,8 +3287,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3154,8 +3331,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3195,8 +3375,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3236,32 +3419,35 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10621000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11211000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10893000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11040000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20282000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20021000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18927000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3277,8 +3463,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3318,43 +3507,46 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45200</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45109</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45018</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44927</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44836</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44745</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44472</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3364,38 +3556,41 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>296000</v>
+      </c>
+      <c r="E81" s="3">
         <v>327000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>438000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>899000</v>
       </c>
-      <c r="G81" s="3">
-        <v>330000</v>
-      </c>
       <c r="H81" s="3">
+        <v>469000</v>
+      </c>
+      <c r="I81" s="3">
         <v>347000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>585000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>604000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1620000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,8 +3600,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3422,35 +3620,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E83" s="3">
         <v>174000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>153000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>300000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>152000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>166000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>152000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>161000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,8 +3662,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3504,8 +3706,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3545,8 +3750,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3586,8 +3794,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3627,8 +3838,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3668,35 +3882,38 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E89" s="3">
         <v>950000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>674000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1544000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>802000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>644000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>736000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>807000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3709,8 +3926,11 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3726,35 +3946,36 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-153000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-223000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-114000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-77000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-55000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-159000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-103000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-76000</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -3767,8 +3988,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3808,8 +4032,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3849,35 +4076,38 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-152000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-265000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-105000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-118000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-167000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-108000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-73000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3890,8 +4120,11 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3907,8 +4140,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3916,7 +4150,7 @@
         <v>-383000</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-383000</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3948,8 +4182,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3989,8 +4226,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4030,8 +4270,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4071,35 +4314,38 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-326000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-383000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-726000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1418000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7388000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-63000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-635000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-675000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4112,35 +4358,38 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E101" s="3">
         <v>18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>20000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-34000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-50000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4153,35 +4402,38 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-227000</v>
+      </c>
+      <c r="E102" s="3">
         <v>320000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-169000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>8155000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>434000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-41000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4192,6 +4444,9 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -656,65 +656,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45200</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44927</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44836</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44745</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44472</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -724,41 +725,44 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3894000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3666000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3915000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7863000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3852000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3767000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3789000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3804000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11321000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -768,41 +772,44 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1635000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1652000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1568000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1665000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3513000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1727000</v>
       </c>
-      <c r="I9" s="3">
-        <v>1700000</v>
-      </c>
       <c r="J9" s="3">
+        <v>1661000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1637000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1646000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4851000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -812,41 +819,44 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2365000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2242000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2098000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2250000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4350000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2125000</v>
       </c>
-      <c r="I10" s="3">
-        <v>2067000</v>
-      </c>
       <c r="J10" s="3">
+        <v>2106000</v>
+      </c>
+      <c r="K10" s="3">
         <v>2152000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2158000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6470000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -856,8 +866,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,41 +887,42 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E12" s="3">
         <v>100000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>133000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>78000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>188000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>89000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>103000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>90000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>94000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>253000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,8 +932,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -962,41 +979,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>560000</v>
+      </c>
+      <c r="E14" s="3">
         <v>111000</v>
       </c>
-      <c r="E14" s="3">
-        <v>251000</v>
-      </c>
       <c r="F14" s="3">
-        <v>135000</v>
+        <v>241000</v>
       </c>
       <c r="G14" s="3">
-        <v>212000</v>
+        <v>133000</v>
       </c>
       <c r="H14" s="3">
-        <v>15000</v>
+        <v>220000</v>
       </c>
       <c r="I14" s="3">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>205000</v>
+      </c>
+      <c r="K14" s="3">
         <v>63000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>102000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1006,8 +1026,11 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1050,8 +1073,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1065,41 +1091,42 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3846000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3344000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3206000</v>
       </c>
-      <c r="F17" s="3">
-        <v>3207000</v>
-      </c>
       <c r="G17" s="3">
-        <v>6533000</v>
+        <v>3205000</v>
       </c>
       <c r="H17" s="3">
+        <v>6521000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3212000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3236000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3026000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3024000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8898000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1109,41 +1136,44 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E18" s="3">
         <v>550000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>460000</v>
       </c>
-      <c r="F18" s="3">
-        <v>708000</v>
-      </c>
       <c r="G18" s="3">
-        <v>1330000</v>
+        <v>710000</v>
       </c>
       <c r="H18" s="3">
+        <v>1342000</v>
+      </c>
+      <c r="I18" s="3">
         <v>640000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>531000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>763000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>780000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2423000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1153,8 +1183,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1171,41 +1204,42 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-14000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>11000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-8000</v>
-      </c>
       <c r="G20" s="3">
-        <v>47000</v>
+        <v>-10000</v>
       </c>
       <c r="H20" s="3">
+        <v>35000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-20000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-19000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1215,41 +1249,44 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>312000</v>
+      </c>
+      <c r="E21" s="3">
         <v>685000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>645000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>853000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1677000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>772000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>678000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>890000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>936000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2957000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,43 +1296,46 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E22" s="3">
         <v>109000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>114000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>115000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>129000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1303,41 +1343,44 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E23" s="3">
         <v>427000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>357000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>585000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1248000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>609000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>512000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>738000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>775000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2408000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,41 +1390,44 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>131000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>147000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>349000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>140000</v>
       </c>
-      <c r="I24" s="3">
-        <v>165000</v>
-      </c>
       <c r="J24" s="3">
+        <v>151000</v>
+      </c>
+      <c r="K24" s="3">
         <v>153000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>171000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>788000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1391,8 +1437,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1435,41 +1484,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E26" s="3">
         <v>296000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>327000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>438000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>899000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>469000</v>
       </c>
-      <c r="I26" s="3">
-        <v>347000</v>
-      </c>
       <c r="J26" s="3">
+        <v>361000</v>
+      </c>
+      <c r="K26" s="3">
         <v>585000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>604000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1620000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1479,41 +1531,44 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E27" s="3">
         <v>296000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>327000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>438000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>899000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>469000</v>
       </c>
-      <c r="I27" s="3">
-        <v>347000</v>
-      </c>
       <c r="J27" s="3">
+        <v>361000</v>
+      </c>
+      <c r="K27" s="3">
         <v>585000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>604000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1620000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1523,8 +1578,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1567,8 +1625,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1672,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1655,8 +1719,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1699,41 +1766,44 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E32" s="3">
         <v>14000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-11000</v>
       </c>
-      <c r="F32" s="3">
-        <v>8000</v>
-      </c>
       <c r="G32" s="3">
-        <v>-47000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="I32" s="3">
         <v>20000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>19000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1743,41 +1813,44 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E33" s="3">
         <v>296000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>327000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>438000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>899000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>469000</v>
       </c>
-      <c r="I33" s="3">
-        <v>347000</v>
-      </c>
       <c r="J33" s="3">
+        <v>361000</v>
+      </c>
+      <c r="K33" s="3">
         <v>585000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>604000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1620000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1787,8 +1860,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1831,41 +1907,44 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E35" s="3">
         <v>296000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>327000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>438000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>899000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>469000</v>
       </c>
-      <c r="I35" s="3">
-        <v>347000</v>
-      </c>
       <c r="J35" s="3">
+        <v>361000</v>
+      </c>
+      <c r="K35" s="3">
         <v>585000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>604000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1620000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1875,46 +1954,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44927</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44836</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44745</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44472</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1924,8 +2006,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1942,8 +2027,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1960,35 +2046,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1014000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1155000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1382000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1062000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1231000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1691000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1231000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>797000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2004,8 +2091,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2048,35 +2138,38 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2240000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2160000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2073000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2109000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2096000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2109000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2122000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2141000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,35 +2185,38 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1849000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1884000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1851000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1885000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2026000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2222000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2226000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2133000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2136,35 +2232,38 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>778000</v>
+      </c>
+      <c r="E45" s="3">
         <v>898000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>832000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>838000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>866000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>417000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>298000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>392000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,35 +2279,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5881000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6097000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6138000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5894000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6219000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6439000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5877000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5463000</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2224,8 +2326,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2268,35 +2373,38 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2127000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2145000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2181000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1872000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1832000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1836000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1820000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1700000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2312,35 +2420,38 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17735000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18410000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18890000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18461000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18759000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19071000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19038000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18315000</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2356,8 +2467,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2400,8 +2514,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2444,35 +2561,38 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>700000</v>
+      </c>
+      <c r="E52" s="3">
         <v>631000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>642000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>850000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>732000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8249000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>581000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>544000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,8 +2608,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2532,35 +2655,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26443000</v>
+      </c>
+      <c r="E54" s="3">
         <v>27283000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27851000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27077000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27542000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>35595000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27316000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26022000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2576,8 +2702,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2594,8 +2723,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2612,35 +2742,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2437000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2602000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2489000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2281000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2354000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1781000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1829000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1745000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2656,26 +2787,29 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1427000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1522000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>599000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>513000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>752000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,8 +2825,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2700,35 +2834,38 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2073000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2042000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2393000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2367000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2193000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2429000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2097000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2122000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2744,35 +2881,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5937000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6166000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5481000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5161000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5299000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4210000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3926000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3867000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2788,29 +2928,32 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7051000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7033000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7687000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7685000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7684000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7676000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2832,35 +2975,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3277000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3463000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3472000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3338000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3519000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3427000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3369000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3228000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2876,8 +3022,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2920,8 +3069,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2964,8 +3116,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3008,35 +3163,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16265000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16662000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16640000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16184000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16502000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15313000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7295000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7095000</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,8 +3210,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3070,8 +3231,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3114,8 +3276,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3158,8 +3323,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3202,8 +3370,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3246,35 +3417,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E72" s="3">
         <v>342000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>429000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>485000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>430000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25521000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25474000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25153000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3290,8 +3464,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3334,8 +3511,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3378,8 +3558,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3422,35 +3605,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10178000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10621000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11211000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10893000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11040000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20282000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20021000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18927000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3652,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3510,46 +3699,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45200</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44927</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44836</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44745</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44472</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3559,41 +3751,44 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E81" s="3">
         <v>296000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>327000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>438000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>899000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>469000</v>
       </c>
-      <c r="I81" s="3">
-        <v>347000</v>
-      </c>
       <c r="J81" s="3">
+        <v>361000</v>
+      </c>
+      <c r="K81" s="3">
         <v>585000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>604000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1620000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3603,8 +3798,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3621,38 +3819,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>141000</v>
+      </c>
+      <c r="E83" s="3">
         <v>149000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>174000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>153000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>300000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>152000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>166000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>152000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>161000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3665,8 +3864,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3709,8 +3911,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3753,8 +3958,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3797,8 +4005,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3841,8 +4052,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3885,38 +4099,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>440000</v>
+      </c>
+      <c r="E89" s="3">
         <v>287000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>950000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>674000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1544000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>802000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>644000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>736000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>807000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3929,8 +4146,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3947,38 +4167,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-153000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-223000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-114000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-77000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-55000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-159000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-103000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-76000</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -3991,8 +4212,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4035,8 +4259,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4079,38 +4306,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-152000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-265000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-105000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-118000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-41000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-167000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-108000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-73000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4123,8 +4353,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4141,8 +4374,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4153,7 +4387,7 @@
         <v>-383000</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-383000</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -4185,8 +4419,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4229,8 +4466,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4273,8 +4513,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4317,38 +4560,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-490000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-326000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-383000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-726000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1418000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7388000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-63000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-635000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-675000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,38 +4607,41 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-36000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>20000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-34000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-50000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4405,38 +4654,41 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-141000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-227000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>320000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-169000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>8155000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>434000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-41000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4447,6 +4699,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,69 +656,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45018</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44927</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44836</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44745</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44472</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,44 +729,47 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3899000</v>
+      </c>
+      <c r="E8" s="3">
         <v>4000000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3894000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3666000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3915000</v>
       </c>
-      <c r="H8" s="3">
-        <v>7863000</v>
-      </c>
       <c r="I8" s="3">
+        <v>4011000</v>
+      </c>
+      <c r="J8" s="3">
         <v>3852000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3767000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3789000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3804000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11321000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -775,44 +779,47 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1613000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1635000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1652000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1568000</v>
-      </c>
       <c r="G9" s="3">
+        <v>1623000</v>
+      </c>
+      <c r="H9" s="3">
         <v>1665000</v>
       </c>
-      <c r="H9" s="3">
-        <v>3513000</v>
-      </c>
       <c r="I9" s="3">
+        <v>1786000</v>
+      </c>
+      <c r="J9" s="3">
         <v>1727000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1661000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1637000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1646000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4851000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -822,44 +829,47 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2286000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2365000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2242000</v>
       </c>
-      <c r="F10" s="3">
-        <v>2098000</v>
-      </c>
       <c r="G10" s="3">
+        <v>2043000</v>
+      </c>
+      <c r="H10" s="3">
         <v>2250000</v>
       </c>
-      <c r="H10" s="3">
-        <v>4350000</v>
-      </c>
       <c r="I10" s="3">
+        <v>2225000</v>
+      </c>
+      <c r="J10" s="3">
         <v>2125000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2106000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2152000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2158000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6470000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -869,8 +879,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,44 +901,45 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E12" s="3">
         <v>105000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>133000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>78000</v>
       </c>
-      <c r="H12" s="3">
-        <v>188000</v>
-      </c>
       <c r="I12" s="3">
+        <v>99000</v>
+      </c>
+      <c r="J12" s="3">
         <v>89000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>103000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>90000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>94000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>253000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +949,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,44 +999,47 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E14" s="3">
         <v>560000</v>
       </c>
-      <c r="E14" s="3">
-        <v>111000</v>
-      </c>
       <c r="F14" s="3">
-        <v>241000</v>
+        <v>142000</v>
       </c>
       <c r="G14" s="3">
-        <v>133000</v>
+        <v>149000</v>
       </c>
       <c r="H14" s="3">
-        <v>220000</v>
+        <v>-6000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-22000</v>
       </c>
       <c r="J14" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K14" s="3">
         <v>205000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>63000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-10000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>102000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1029,31 +1049,34 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>182000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>149000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>174000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>153000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>148000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>152000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,8 +1099,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1092,44 +1118,45 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3846000</v>
+        <v>3210000</v>
       </c>
       <c r="E17" s="3">
-        <v>3344000</v>
+        <v>3285000</v>
       </c>
       <c r="F17" s="3">
-        <v>3206000</v>
+        <v>3232000</v>
       </c>
       <c r="G17" s="3">
-        <v>3205000</v>
+        <v>3075000</v>
       </c>
       <c r="H17" s="3">
-        <v>6521000</v>
+        <v>3202000</v>
       </c>
       <c r="I17" s="3">
-        <v>3212000</v>
+        <v>3331000</v>
       </c>
       <c r="J17" s="3">
+        <v>3221000</v>
+      </c>
+      <c r="K17" s="3">
         <v>3236000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3026000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3024000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8898000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1139,44 +1166,47 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>154000</v>
+        <v>689000</v>
       </c>
       <c r="E18" s="3">
-        <v>550000</v>
+        <v>715000</v>
       </c>
       <c r="F18" s="3">
-        <v>460000</v>
+        <v>662000</v>
       </c>
       <c r="G18" s="3">
-        <v>710000</v>
+        <v>591000</v>
       </c>
       <c r="H18" s="3">
-        <v>1342000</v>
+        <v>713000</v>
       </c>
       <c r="I18" s="3">
-        <v>640000</v>
+        <v>680000</v>
       </c>
       <c r="J18" s="3">
+        <v>631000</v>
+      </c>
+      <c r="K18" s="3">
         <v>531000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>763000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>780000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2423000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1186,8 +1216,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1205,44 +1238,45 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>17000</v>
+        <v>-19000</v>
       </c>
       <c r="E20" s="3">
-        <v>-14000</v>
+        <v>-2000</v>
       </c>
       <c r="F20" s="3">
-        <v>11000</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>-10000</v>
+        <v>-11000</v>
       </c>
       <c r="H20" s="3">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="I20" s="3">
-        <v>-20000</v>
+        <v>10000</v>
       </c>
       <c r="J20" s="3">
+        <v>23000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-19000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-25000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1252,44 +1286,47 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>312000</v>
+        <v>890000</v>
       </c>
       <c r="E21" s="3">
-        <v>685000</v>
+        <v>858000</v>
       </c>
       <c r="F21" s="3">
-        <v>645000</v>
+        <v>813000</v>
       </c>
       <c r="G21" s="3">
-        <v>853000</v>
+        <v>776000</v>
       </c>
       <c r="H21" s="3">
-        <v>1677000</v>
+        <v>832000</v>
       </c>
       <c r="I21" s="3">
-        <v>772000</v>
+        <v>818000</v>
       </c>
       <c r="J21" s="3">
+        <v>760000</v>
+      </c>
+      <c r="K21" s="3">
         <v>678000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>890000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>936000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2957000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,46 +1336,49 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E22" s="3">
         <v>106000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>109000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>114000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>115000</v>
       </c>
-      <c r="H22" s="3">
-        <v>129000</v>
-      </c>
       <c r="I22" s="3">
+        <v>118000</v>
+      </c>
+      <c r="J22" s="3">
         <v>11000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1346,44 +1386,47 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E23" s="3">
         <v>65000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>427000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>357000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>585000</v>
       </c>
-      <c r="H23" s="3">
-        <v>1248000</v>
-      </c>
       <c r="I23" s="3">
+        <v>639000</v>
+      </c>
+      <c r="J23" s="3">
         <v>609000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>512000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>738000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>775000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2408000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,44 +1436,47 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E24" s="3">
         <v>7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>131000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>147000</v>
       </c>
-      <c r="H24" s="3">
-        <v>349000</v>
-      </c>
       <c r="I24" s="3">
+        <v>209000</v>
+      </c>
+      <c r="J24" s="3">
         <v>140000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>151000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>153000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>171000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>788000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,8 +1486,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1487,44 +1536,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E26" s="3">
         <v>58000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>296000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>327000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>438000</v>
       </c>
-      <c r="H26" s="3">
-        <v>899000</v>
-      </c>
       <c r="I26" s="3">
+        <v>430000</v>
+      </c>
+      <c r="J26" s="3">
         <v>469000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>361000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>585000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>604000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1620000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1534,44 +1586,47 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E27" s="3">
         <v>58000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>296000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>327000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>438000</v>
       </c>
-      <c r="H27" s="3">
-        <v>899000</v>
-      </c>
       <c r="I27" s="3">
+        <v>430000</v>
+      </c>
+      <c r="J27" s="3">
         <v>469000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>361000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>585000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>604000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1620000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1636,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1628,8 +1686,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1736,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,8 +1786,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1769,44 +1836,47 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-17000</v>
+        <v>19000</v>
       </c>
       <c r="E32" s="3">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="3">
-        <v>-11000</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="3">
-        <v>-35000</v>
+        <v>-34000</v>
       </c>
       <c r="I32" s="3">
-        <v>20000</v>
+        <v>-10000</v>
       </c>
       <c r="J32" s="3">
+        <v>-23000</v>
+      </c>
+      <c r="K32" s="3">
         <v>19000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>25000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1816,44 +1886,47 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E33" s="3">
         <v>58000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>296000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>327000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>438000</v>
       </c>
-      <c r="H33" s="3">
-        <v>899000</v>
-      </c>
       <c r="I33" s="3">
+        <v>430000</v>
+      </c>
+      <c r="J33" s="3">
         <v>469000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>361000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>585000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>604000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1620000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,8 +1936,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1910,44 +1986,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E35" s="3">
         <v>58000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>296000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>327000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>438000</v>
       </c>
-      <c r="H35" s="3">
-        <v>899000</v>
-      </c>
       <c r="I35" s="3">
+        <v>430000</v>
+      </c>
+      <c r="J35" s="3">
         <v>469000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>361000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>585000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>604000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1620000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,49 +2036,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45018</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44927</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44836</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44745</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44472</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2009,8 +2091,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2028,8 +2113,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2047,38 +2133,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1057000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1014000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1155000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1382000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1062000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1231000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1691000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1231000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>797000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2181,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2141,38 +2231,41 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2394000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2240000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2160000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2073000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2109000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2096000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2109000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2122000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2141000</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2188,38 +2281,41 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1820000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1849000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1884000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1851000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1885000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2026000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2222000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2226000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2133000</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,38 +2331,41 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>778000</v>
+        <v>228000</v>
       </c>
       <c r="E45" s="3">
-        <v>898000</v>
+        <v>250000</v>
       </c>
       <c r="F45" s="3">
-        <v>832000</v>
+        <v>275000</v>
       </c>
       <c r="G45" s="3">
-        <v>838000</v>
+        <v>283000</v>
       </c>
       <c r="H45" s="3">
-        <v>866000</v>
+        <v>252000</v>
       </c>
       <c r="I45" s="3">
-        <v>417000</v>
+        <v>241000</v>
       </c>
       <c r="J45" s="3">
+        <v>206000</v>
+      </c>
+      <c r="K45" s="3">
         <v>298000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>392000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2282,38 +2381,41 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5941000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5881000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6097000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6138000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5894000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6219000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6439000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5877000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5463000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2329,31 +2431,34 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>76000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>78000</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2376,38 +2481,41 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1898000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2127000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2145000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2181000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1872000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1832000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1836000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1820000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1700000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2423,38 +2531,41 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18184000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17735000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18410000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18890000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18461000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18759000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19071000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19038000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18315000</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2581,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2517,8 +2631,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2564,38 +2681,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>700000</v>
+        <v>633000</v>
       </c>
       <c r="E52" s="3">
-        <v>631000</v>
+        <v>453000</v>
       </c>
       <c r="F52" s="3">
-        <v>642000</v>
+        <v>419000</v>
       </c>
       <c r="G52" s="3">
-        <v>850000</v>
+        <v>413000</v>
       </c>
       <c r="H52" s="3">
-        <v>732000</v>
+        <v>618000</v>
       </c>
       <c r="I52" s="3">
-        <v>8249000</v>
+        <v>511000</v>
       </c>
       <c r="J52" s="3">
+        <v>8025000</v>
+      </c>
+      <c r="K52" s="3">
         <v>581000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>544000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,8 +2731,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2658,38 +2781,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26925000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26443000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27283000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27851000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27077000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27542000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>35595000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27316000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26022000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2705,8 +2831,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2724,8 +2853,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2743,38 +2873,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2274000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2437000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2602000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2489000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2281000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2354000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1781000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1829000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1745000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,31 +2921,34 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1427000</v>
+        <v>1688000</v>
       </c>
       <c r="E58" s="3">
-        <v>1522000</v>
+        <v>1467000</v>
       </c>
       <c r="F58" s="3">
-        <v>599000</v>
+        <v>1566000</v>
       </c>
       <c r="G58" s="3">
-        <v>513000</v>
+        <v>643000</v>
       </c>
       <c r="H58" s="3">
-        <v>752000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>559000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>32000</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2828,8 +2962,8 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2837,38 +2971,41 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2073000</v>
+        <v>249000</v>
       </c>
       <c r="E59" s="3">
-        <v>2042000</v>
+        <v>272000</v>
       </c>
       <c r="F59" s="3">
-        <v>2393000</v>
+        <v>334000</v>
       </c>
       <c r="G59" s="3">
-        <v>2367000</v>
+        <v>142000</v>
       </c>
       <c r="H59" s="3">
-        <v>2193000</v>
+        <v>383000</v>
       </c>
       <c r="I59" s="3">
-        <v>2429000</v>
+        <v>239000</v>
       </c>
       <c r="J59" s="3">
+        <v>604000</v>
+      </c>
+      <c r="K59" s="3">
         <v>2097000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2122000</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2884,38 +3021,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5946000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5937000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6166000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5481000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5161000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5299000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4210000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3926000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3867000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2931,31 +3071,34 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7051000</v>
+        <v>7139000</v>
       </c>
       <c r="E61" s="3">
-        <v>7033000</v>
+        <v>7139000</v>
       </c>
       <c r="F61" s="3">
-        <v>7687000</v>
+        <v>7131000</v>
       </c>
       <c r="G61" s="3">
-        <v>7685000</v>
+        <v>7784000</v>
       </c>
       <c r="H61" s="3">
-        <v>7684000</v>
+        <v>7791000</v>
       </c>
       <c r="I61" s="3">
-        <v>7676000</v>
+        <v>7804000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>7761000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2978,38 +3121,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3277000</v>
+        <v>456000</v>
       </c>
       <c r="E62" s="3">
-        <v>3463000</v>
+        <v>447000</v>
       </c>
       <c r="F62" s="3">
-        <v>3472000</v>
+        <v>443000</v>
       </c>
       <c r="G62" s="3">
-        <v>3338000</v>
+        <v>394000</v>
       </c>
       <c r="H62" s="3">
-        <v>3519000</v>
+        <v>463000</v>
       </c>
       <c r="I62" s="3">
-        <v>3427000</v>
+        <v>473000</v>
       </c>
       <c r="J62" s="3">
+        <v>431000</v>
+      </c>
+      <c r="K62" s="3">
         <v>3369000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3228000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,8 +3171,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3072,8 +3221,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3119,8 +3271,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3166,38 +3321,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16281000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16265000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16662000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16640000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16184000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16502000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15313000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7295000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7095000</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3213,8 +3371,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3232,8 +3393,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3279,8 +3441,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3326,8 +3491,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3373,8 +3541,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3420,38 +3591,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>342000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>429000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>485000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>430000</v>
       </c>
-      <c r="I72" s="3">
-        <v>25521000</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>25474000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>25153000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3641,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3514,8 +3691,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3561,8 +3741,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3608,38 +3791,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10644000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10178000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10621000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11211000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10893000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11040000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20282000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20021000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18927000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3655,8 +3841,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3702,49 +3891,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45018</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44927</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44836</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44745</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44472</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3754,44 +3946,47 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>383000</v>
+      </c>
+      <c r="E81" s="3">
         <v>58000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>296000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>327000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>438000</v>
       </c>
-      <c r="H81" s="3">
-        <v>899000</v>
-      </c>
       <c r="I81" s="3">
+        <v>430000</v>
+      </c>
+      <c r="J81" s="3">
         <v>469000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>361000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>585000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>604000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1620000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3801,8 +3996,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3820,41 +4018,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>141000</v>
+        <v>71000</v>
       </c>
       <c r="E83" s="3">
-        <v>149000</v>
+        <v>69000</v>
       </c>
       <c r="F83" s="3">
-        <v>174000</v>
+        <v>71000</v>
       </c>
       <c r="G83" s="3">
-        <v>153000</v>
+        <v>83000</v>
       </c>
       <c r="H83" s="3">
-        <v>300000</v>
+        <v>69000</v>
       </c>
       <c r="I83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K83" s="3">
+        <v>166000</v>
+      </c>
+      <c r="L83" s="3">
         <v>152000</v>
       </c>
-      <c r="J83" s="3">
-        <v>166000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>152000</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>161000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +4066,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3914,8 +4116,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3961,8 +4166,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4008,8 +4216,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4055,8 +4266,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4102,41 +4316,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E89" s="3">
         <v>440000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>287000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>950000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>674000</v>
       </c>
-      <c r="H89" s="3">
-        <v>1544000</v>
-      </c>
       <c r="I89" s="3">
+        <v>742000</v>
+      </c>
+      <c r="J89" s="3">
         <v>802000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>644000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>736000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>807000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4149,8 +4366,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4168,41 +4388,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-153000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-223000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-114000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-77000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-55000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-159000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-103000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-76000</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4215,8 +4436,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4262,8 +4486,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4309,41 +4536,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-56000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-85000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-152000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-265000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-105000</v>
       </c>
-      <c r="H94" s="3">
-        <v>-118000</v>
-      </c>
       <c r="I94" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-41000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-167000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-108000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-73000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4356,8 +4586,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4375,31 +4608,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-383000</v>
+        <v>393000</v>
       </c>
       <c r="E96" s="3">
-        <v>-383000</v>
+        <v>383000</v>
       </c>
       <c r="F96" s="3">
-        <v>-383000</v>
+        <v>383000</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>383000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>383000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>13788000</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4422,8 +4656,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4469,8 +4706,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4516,8 +4756,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4563,41 +4806,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-490000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-326000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-383000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-726000</v>
       </c>
-      <c r="H100" s="3">
-        <v>-1418000</v>
-      </c>
       <c r="I100" s="3">
+        <v>-8806000</v>
+      </c>
+      <c r="J100" s="3">
         <v>7388000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-63000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-635000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-675000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4610,41 +4856,44 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-6000</v>
+        <v>-12000</v>
       </c>
       <c r="E101" s="3">
-        <v>-36000</v>
+        <v>-14000</v>
       </c>
       <c r="F101" s="3">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="G101" s="3">
-        <v>-12000</v>
+        <v>20000</v>
       </c>
       <c r="H101" s="3">
-        <v>-8000</v>
+        <v>-34000</v>
       </c>
       <c r="I101" s="3">
-        <v>6000</v>
+        <v>-50000</v>
       </c>
       <c r="J101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K101" s="3">
         <v>20000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-34000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-50000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4657,41 +4906,44 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-141000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-227000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>320000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-169000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>-8155000</v>
+      </c>
+      <c r="J102" s="3">
         <v>8155000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>434000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4702,6 +4954,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,73 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44836</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44745</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44472</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,47 +732,50 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3662000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3899000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4000000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3894000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3666000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3915000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4011000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3852000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3767000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3789000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3804000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11321000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,47 +785,50 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1584000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1613000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1635000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1652000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1623000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1665000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1786000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1727000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1661000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1637000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1646000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4851000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -832,47 +838,50 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2078000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2286000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2365000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2242000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2043000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2250000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2225000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2125000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2106000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2152000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2158000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6470000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,8 +891,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,47 +914,48 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E12" s="3">
         <v>97000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>105000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>133000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>78000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>99000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>89000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>103000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>90000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>94000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>253000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -952,8 +965,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1002,47 +1018,50 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>421000</v>
+      </c>
+      <c r="E14" s="3">
         <v>35000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>560000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>142000</v>
       </c>
-      <c r="G14" s="3">
-        <v>149000</v>
-      </c>
       <c r="H14" s="3">
+        <v>392000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-6000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-22000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>205000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>63000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-10000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>102000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1052,35 +1071,38 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E15" s="3">
         <v>182000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>141000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>149000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>174000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>153000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>148000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>152000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1102,8 +1124,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1119,47 +1144,48 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2804000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3210000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3285000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3232000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3075000</v>
-      </c>
       <c r="H17" s="3">
+        <v>2832000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3202000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3331000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3221000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3236000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3026000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3024000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8898000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1169,47 +1195,50 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E18" s="3">
         <v>689000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>715000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>662000</v>
       </c>
-      <c r="G18" s="3">
-        <v>591000</v>
-      </c>
       <c r="H18" s="3">
+        <v>834000</v>
+      </c>
+      <c r="I18" s="3">
         <v>713000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>680000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>631000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>531000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>763000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>780000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2423000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1219,8 +1248,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1239,47 +1271,48 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-2000</v>
       </c>
       <c r="F20" s="3">
         <v>-2000</v>
       </c>
       <c r="G20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H20" s="3">
         <v>-11000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>34000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>23000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-19000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1289,47 +1322,50 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1012000</v>
+      </c>
+      <c r="E21" s="3">
         <v>890000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>858000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>813000</v>
       </c>
-      <c r="G21" s="3">
-        <v>776000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1019000</v>
+      </c>
+      <c r="I21" s="3">
         <v>832000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>818000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>760000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>678000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>890000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>936000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2957000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1339,8 +1375,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,40 +1387,40 @@
         <v>108000</v>
       </c>
       <c r="E22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="F22" s="3">
         <v>106000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>109000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>114000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>115000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>118000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11000</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1389,47 +1428,50 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>346000</v>
+      </c>
+      <c r="E23" s="3">
         <v>577000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>65000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>427000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>357000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>585000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>639000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>609000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>512000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>738000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>775000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2408000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,47 +1481,50 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E24" s="3">
         <v>194000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>131000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>30000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>147000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>209000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>140000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>151000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>153000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>171000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>788000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1489,8 +1534,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1539,47 +1587,50 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E26" s="3">
         <v>383000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>58000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>296000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>327000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>438000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>430000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>469000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>361000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>585000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>604000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1620000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1589,47 +1640,50 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E27" s="3">
         <v>383000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>58000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>296000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>327000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>438000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>430000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>469000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>361000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>585000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>604000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1620000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1639,8 +1693,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1689,8 +1746,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1739,8 +1799,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1789,8 +1852,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1839,47 +1905,50 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>19000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>2000</v>
       </c>
       <c r="F32" s="3">
         <v>2000</v>
       </c>
       <c r="G32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H32" s="3">
         <v>11000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-34000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-23000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>19000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1889,47 +1958,50 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E33" s="3">
         <v>383000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>58000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>296000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>327000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>438000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>430000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>469000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>361000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>585000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>604000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1620000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1939,8 +2011,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1989,47 +2064,50 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E35" s="3">
         <v>383000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>58000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>296000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>327000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>438000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>430000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>469000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>361000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>585000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>604000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1620000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,52 +2117,55 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44836</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44745</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44472</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2175,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2114,8 +2198,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2134,41 +2219,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1070000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1057000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1014000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1155000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1382000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1062000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1231000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1691000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1231000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>797000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,8 +2270,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2234,41 +2323,44 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2165000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2394000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2240000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2160000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2073000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2109000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2096000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2109000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2122000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2141000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,41 +2376,44 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1591000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1820000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1849000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1884000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1851000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1885000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2026000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2222000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2226000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2133000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,41 +2429,44 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>257000</v>
+      </c>
+      <c r="E45" s="3">
         <v>228000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>250000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>275000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>283000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>252000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>241000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>206000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>298000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>392000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2384,41 +2482,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5525000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5941000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5881000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6097000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6138000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5894000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6219000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6439000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5877000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5463000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,13 +2535,16 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>41000</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
         <v>41000</v>
@@ -2449,20 +2553,20 @@
         <v>41000</v>
       </c>
       <c r="G47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="H47" s="3">
         <v>71000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>76000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>78000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>56000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2484,41 +2588,44 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1960000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1898000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2127000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2145000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2181000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1872000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1832000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1836000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1820000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1700000</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2534,41 +2641,44 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17317000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18184000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17735000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18410000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18890000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18461000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18759000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19071000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19038000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18315000</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2584,8 +2694,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2634,8 +2747,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2684,41 +2800,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>615000</v>
+      </c>
+      <c r="E52" s="3">
         <v>633000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>453000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>419000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>413000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>618000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>511000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8025000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>581000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>544000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2734,8 +2853,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2784,41 +2906,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25601000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26925000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26443000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27283000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27851000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27077000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27542000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>35595000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27316000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26022000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2834,8 +2959,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2854,8 +2982,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2874,41 +3003,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2254000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2274000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2437000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2602000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2489000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2281000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2354000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1781000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1829000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1745000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,35 +3054,38 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1588000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1688000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1467000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1566000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>643000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>559000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>799000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3098,8 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -2974,41 +3107,44 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E59" s="3">
         <v>249000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>272000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>334000</v>
       </c>
-      <c r="G59" s="3">
-        <v>142000</v>
-      </c>
       <c r="H59" s="3">
+        <v>255000</v>
+      </c>
+      <c r="I59" s="3">
         <v>383000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>239000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>604000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2097000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2122000</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,41 +3160,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5739000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5946000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5937000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6166000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5481000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5161000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5299000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4210000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3926000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3867000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3074,35 +3213,38 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7139000</v>
+        <v>7131000</v>
       </c>
       <c r="E61" s="3">
         <v>7139000</v>
       </c>
       <c r="F61" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="G61" s="3">
         <v>7131000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7784000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7791000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7804000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7761000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3124,41 +3266,44 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>460000</v>
+      </c>
+      <c r="E62" s="3">
         <v>456000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>447000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>443000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>394000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>463000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>473000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>431000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3369000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3228000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3174,8 +3319,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3224,8 +3372,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3274,8 +3425,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3324,41 +3478,44 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15933000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16281000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16265000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16662000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16640000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16184000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16502000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15313000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7295000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7095000</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,8 +3531,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3394,8 +3554,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3444,8 +3605,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3494,8 +3658,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3544,8 +3711,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3594,41 +3764,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>342000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>429000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>485000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>430000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>25474000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>25153000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3817,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3694,8 +3870,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3744,8 +3923,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3794,41 +3976,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9668000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10644000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10178000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10621000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11211000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10893000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11040000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20282000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20021000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18927000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3844,8 +4029,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3894,52 +4082,55 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44836</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44745</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44472</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3949,47 +4140,50 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>293000</v>
+      </c>
+      <c r="E81" s="3">
         <v>383000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>58000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>296000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>327000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>438000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>430000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>469000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>361000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>585000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>604000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1620000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4193,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4019,44 +4216,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>94000</v>
+      </c>
+      <c r="E83" s="3">
         <v>71000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>71000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>83000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>69000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>72000</v>
       </c>
       <c r="J83" s="3">
         <v>72000</v>
       </c>
       <c r="K83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="L83" s="3">
         <v>166000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>152000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>161000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4267,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4119,8 +4320,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4169,8 +4373,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4219,8 +4426,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4269,8 +4479,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4319,44 +4532,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>793000</v>
+      </c>
+      <c r="E89" s="3">
         <v>249000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>440000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>287000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>950000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>674000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>742000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>802000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>644000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>736000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>807000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4369,8 +4585,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4389,44 +4608,45 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-138000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-59000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-153000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-223000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-114000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-77000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-55000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-159000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-103000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-76000</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4439,8 +4659,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4489,8 +4712,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4539,44 +4765,47 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-132000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-56000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-152000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-265000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-105000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-77000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-41000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-167000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-108000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-73000</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4589,8 +4818,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4609,8 +4841,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4618,7 +4851,7 @@
         <v>393000</v>
       </c>
       <c r="E96" s="3">
-        <v>383000</v>
+        <v>393000</v>
       </c>
       <c r="F96" s="3">
         <v>383000</v>
@@ -4626,17 +4859,17 @@
       <c r="G96" s="3">
         <v>383000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3">
         <v>383000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>13788000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4659,8 +4892,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4709,8 +4945,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4759,8 +4998,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4809,44 +5051,47 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-587000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-162000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-490000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-326000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-383000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-726000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8806000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7388000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-63000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-635000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-675000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4859,44 +5104,47 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-14000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>20000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-34000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-50000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>20000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-34000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-50000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4909,44 +5157,47 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>43000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-141000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-227000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>320000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-169000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8155000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>8155000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>434000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9000</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4957,6 +5208,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,76 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45018</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44836</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44745</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44472</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -735,50 +736,53 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3741000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3662000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3899000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4000000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3894000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3666000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3915000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4011000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3852000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3767000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3789000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3804000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11321000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -788,50 +792,53 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1584000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1613000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1635000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1652000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1646000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1623000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1665000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1786000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1727000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1661000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1637000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1646000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4851000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,50 +848,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2078000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2286000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2365000</v>
       </c>
-      <c r="G10" s="3">
-        <v>2242000</v>
-      </c>
       <c r="H10" s="3">
+        <v>2248000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2043000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2250000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2225000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2125000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2106000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2152000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2158000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6470000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,8 +904,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -915,50 +928,51 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E12" s="3">
         <v>106000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>97000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>105000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>100000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>133000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>78000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>99000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>89000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>103000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>90000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>94000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>253000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -968,8 +982,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1021,50 +1038,53 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E14" s="3">
         <v>421000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>35000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>560000</v>
       </c>
-      <c r="G14" s="3">
-        <v>142000</v>
-      </c>
       <c r="H14" s="3">
+        <v>149000</v>
+      </c>
+      <c r="I14" s="3">
         <v>392000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-6000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-22000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>205000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>63000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-10000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>102000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1074,38 +1094,41 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E15" s="3">
         <v>150000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>182000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>141000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>149000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>174000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>153000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>148000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>152000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1127,8 +1150,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1145,50 +1171,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3116000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2804000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3210000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3285000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3232000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3226000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2832000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3202000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3331000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3221000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3236000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3026000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3024000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8898000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1198,50 +1225,53 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>625000</v>
+      </c>
+      <c r="E18" s="3">
         <v>858000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>689000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>715000</v>
       </c>
-      <c r="G18" s="3">
-        <v>662000</v>
-      </c>
       <c r="H18" s="3">
+        <v>668000</v>
+      </c>
+      <c r="I18" s="3">
         <v>834000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>713000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>680000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>631000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>531000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>763000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>780000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2423000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1251,8 +1281,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1272,50 +1305,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-19000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2000</v>
       </c>
       <c r="G20" s="3">
         <v>-2000</v>
       </c>
       <c r="H20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-11000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>34000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>23000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-19000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1325,50 +1359,53 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1012000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>890000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>858000</v>
       </c>
-      <c r="G21" s="3">
-        <v>813000</v>
-      </c>
       <c r="H21" s="3">
+        <v>820000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1019000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>832000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>818000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>760000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>678000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>890000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>936000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2957000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,52 +1415,55 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>108000</v>
+        <v>107000</v>
       </c>
       <c r="E22" s="3">
         <v>108000</v>
       </c>
       <c r="F22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="G22" s="3">
         <v>106000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>109000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>114000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>115000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>118000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11000</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1431,50 +1471,53 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>458000</v>
+      </c>
+      <c r="E23" s="3">
         <v>346000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>577000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>65000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>427000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>357000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>585000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>639000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>609000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>512000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>738000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>775000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2408000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1484,50 +1527,53 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E24" s="3">
         <v>53000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>194000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>131000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>30000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>147000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>209000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>140000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>151000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>153000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>171000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>788000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,8 +1583,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1590,50 +1639,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E26" s="3">
         <v>293000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>383000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>58000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>296000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>327000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>438000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>430000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>469000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>361000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>585000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>604000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1620000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1643,50 +1695,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E27" s="3">
         <v>293000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>383000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>58000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>296000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>327000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>438000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>430000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>469000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>361000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>585000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>604000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1620000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1696,8 +1751,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1749,8 +1807,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1802,8 +1863,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1855,8 +1919,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1908,50 +1975,53 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>19000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2000</v>
       </c>
       <c r="G32" s="3">
         <v>2000</v>
       </c>
       <c r="H32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="3">
         <v>11000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-34000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-23000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>19000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1961,50 +2031,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E33" s="3">
         <v>293000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>383000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>58000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>296000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>327000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>438000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>430000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>469000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>361000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>585000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>604000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1620000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2014,8 +2087,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2067,50 +2143,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E35" s="3">
         <v>293000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>383000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>58000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>296000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>327000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>438000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>430000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>469000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>361000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>585000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>604000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1620000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2120,55 +2199,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45018</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44836</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44745</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44472</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2178,8 +2260,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2199,8 +2284,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2220,44 +2306,45 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1057000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1070000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1057000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1014000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1155000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1382000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1062000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1231000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1691000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1231000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>797000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2273,8 +2360,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2326,44 +2416,47 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2312000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2165000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2394000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2240000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2160000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2073000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2109000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2096000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2109000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2122000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2141000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2379,44 +2472,47 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1680000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1591000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1820000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1849000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1884000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1851000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1885000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2026000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2222000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2226000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2133000</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2432,44 +2528,47 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E45" s="3">
         <v>257000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>228000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>250000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>275000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>283000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>252000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>241000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>206000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>298000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>392000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,44 +2584,47 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5710000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5525000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5941000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5881000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6097000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6138000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5894000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6219000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6439000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5877000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5463000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2538,16 +2640,19 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>41000</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>41000</v>
@@ -2556,20 +2661,20 @@
         <v>41000</v>
       </c>
       <c r="H47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="I47" s="3">
         <v>71000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>76000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>78000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>56000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2591,44 +2696,47 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1927000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1960000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1898000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2127000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2145000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2181000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1872000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1832000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1836000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1820000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1700000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2644,44 +2752,47 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17722000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17317000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18184000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17735000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18410000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18890000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18461000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18759000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19071000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19038000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18315000</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2808,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2750,8 +2864,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2803,44 +2920,47 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>699000</v>
+      </c>
+      <c r="E52" s="3">
         <v>615000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>633000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>453000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>419000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>413000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>618000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>511000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8025000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>581000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>544000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +2976,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2909,44 +3032,47 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26257000</v>
+      </c>
+      <c r="E54" s="3">
         <v>25601000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26925000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26443000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27283000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27851000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27077000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27542000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35595000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27316000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26022000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3088,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2983,8 +3112,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3004,44 +3134,45 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2332000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2254000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2274000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2437000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2602000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2489000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2281000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2354000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1781000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1829000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1745000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3057,38 +3188,41 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2466000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1588000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1688000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1467000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1566000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>643000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>559000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>799000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3101,8 +3235,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3110,44 +3244,47 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E59" s="3">
         <v>156000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>249000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>272000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>334000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>255000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>383000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>239000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>604000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2097000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2122000</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3163,44 +3300,47 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6666000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5739000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5946000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5937000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6166000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5481000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5161000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5299000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4210000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3926000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3867000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,38 +3356,41 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6385000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7131000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>7139000</v>
       </c>
       <c r="F61" s="3">
         <v>7139000</v>
       </c>
       <c r="G61" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="H61" s="3">
         <v>7131000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7784000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7791000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7804000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7761000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3269,44 +3412,47 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>483000</v>
+      </c>
+      <c r="E62" s="3">
         <v>460000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>456000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>447000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>443000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>394000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>463000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>473000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>431000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3369000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3228000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3322,8 +3468,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3375,8 +3524,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3428,8 +3580,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3481,44 +3636,47 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16204000</v>
+      </c>
+      <c r="E66" s="3">
         <v>15933000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16281000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16265000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16662000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16640000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16184000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16502000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15313000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7295000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7095000</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,8 +3692,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3555,8 +3716,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3608,8 +3770,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3661,8 +3826,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3714,8 +3882,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3767,44 +3938,47 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-163000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-93000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>17000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>342000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>429000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>485000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>430000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>25474000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>25153000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3820,8 +3994,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3873,8 +4050,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3926,8 +4106,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3979,44 +4162,47 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10053000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9668000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10644000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10178000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10621000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11211000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10893000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11040000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20282000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20021000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>18927000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4032,8 +4218,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4085,55 +4274,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45018</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44836</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44745</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44472</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4143,50 +4335,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>322000</v>
+      </c>
+      <c r="E81" s="3">
         <v>293000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>383000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>58000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>296000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>327000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>438000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>430000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>469000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>361000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>585000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>604000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1620000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4196,8 +4391,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4217,47 +4415,48 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E83" s="3">
         <v>94000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>71000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>71000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>83000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>69000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>72000</v>
       </c>
       <c r="K83" s="3">
         <v>72000</v>
       </c>
       <c r="L83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="M83" s="3">
         <v>166000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>152000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>161000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4270,8 +4469,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4323,8 +4525,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4376,8 +4581,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4429,8 +4637,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4482,8 +4693,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4535,47 +4749,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>428000</v>
+      </c>
+      <c r="E89" s="3">
         <v>793000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>249000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>440000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>287000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>950000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>674000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>742000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>802000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>644000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>736000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>807000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4588,8 +4805,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4609,47 +4829,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-179000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-138000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-59000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-90000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-153000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-223000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-114000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-77000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-55000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-159000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-103000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-76000</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -4662,8 +4883,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4715,8 +4939,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4768,47 +4995,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-167000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-132000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-56000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-85000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-152000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-265000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-105000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-77000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-41000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-167000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-73000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4821,8 +5051,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4842,37 +5075,38 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>393000</v>
+        <v>392000</v>
       </c>
       <c r="E96" s="3">
         <v>393000</v>
       </c>
       <c r="F96" s="3">
-        <v>383000</v>
+        <v>393000</v>
       </c>
       <c r="G96" s="3">
         <v>383000</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="H96" s="3">
         <v>383000</v>
       </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="J96" s="3">
+        <v>383000</v>
+      </c>
+      <c r="K96" s="3">
         <v>13788000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4895,8 +5129,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4948,8 +5185,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5001,8 +5241,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5054,47 +5297,50 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-310000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-587000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-162000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-490000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-326000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-383000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-726000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8806000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7388000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-63000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-635000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-675000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5107,47 +5353,50 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E101" s="3">
         <v>18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-14000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>20000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-34000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-50000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-34000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-50000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5160,47 +5409,50 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>43000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-141000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-227000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>320000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-169000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-8155000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8155000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>434000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-41000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>9000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5211,6 +5463,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,80 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45018</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44927</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44836</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44745</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44472</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -739,53 +740,56 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3839000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3741000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3662000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3899000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4000000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3894000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3666000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3915000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4011000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3852000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3767000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3789000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3804000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11321000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -795,53 +799,56 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1567000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1584000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1613000</v>
       </c>
-      <c r="G9" s="3">
-        <v>1635000</v>
-      </c>
       <c r="H9" s="3">
+        <v>1626000</v>
+      </c>
+      <c r="I9" s="3">
         <v>1646000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1623000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1665000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1786000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1727000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1661000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1637000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1646000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4851000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,53 +858,56 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2267000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2174000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2078000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2286000</v>
       </c>
-      <c r="G10" s="3">
-        <v>2365000</v>
-      </c>
       <c r="H10" s="3">
+        <v>2374000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2248000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2043000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2250000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2225000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2125000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2106000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2152000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2158000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6470000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -907,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,53 +942,54 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E12" s="3">
         <v>99000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>106000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>97000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>105000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>133000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>78000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>99000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>89000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>103000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>90000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>94000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>253000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1041,53 +1058,56 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E14" s="3">
         <v>67000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>421000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>35000</v>
       </c>
-      <c r="G14" s="3">
-        <v>560000</v>
-      </c>
       <c r="H14" s="3">
+        <v>568000</v>
+      </c>
+      <c r="I14" s="3">
         <v>149000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>392000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-6000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-22000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>205000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>63000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-10000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>102000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1097,41 +1117,44 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E15" s="3">
         <v>136000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>150000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>182000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>141000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>149000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>174000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>153000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>148000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>152000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1153,8 +1176,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1172,53 +1198,54 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3079000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3116000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2804000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3210000</v>
       </c>
-      <c r="G17" s="3">
-        <v>3285000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3278000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3226000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2832000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3202000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3331000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3221000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3236000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3026000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3024000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8898000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1228,53 +1255,56 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>760000</v>
+      </c>
+      <c r="E18" s="3">
         <v>625000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>858000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>689000</v>
       </c>
-      <c r="G18" s="3">
-        <v>715000</v>
-      </c>
       <c r="H18" s="3">
+        <v>722000</v>
+      </c>
+      <c r="I18" s="3">
         <v>668000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>834000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>713000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>680000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>631000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>531000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>763000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>780000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2423000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1314,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1306,53 +1339,54 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
         <v>6000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-19000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2000</v>
       </c>
       <c r="H20" s="3">
         <v>-3000</v>
       </c>
       <c r="I20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-11000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>34000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-19000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1362,53 +1396,56 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>892000</v>
+      </c>
+      <c r="E21" s="3">
         <v>755000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1012000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>890000</v>
       </c>
-      <c r="G21" s="3">
-        <v>858000</v>
-      </c>
       <c r="H21" s="3">
+        <v>866000</v>
+      </c>
+      <c r="I21" s="3">
         <v>820000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1019000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>832000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>818000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>760000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>678000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>890000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>936000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2957000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1418,8 +1455,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1427,46 +1467,46 @@
         <v>107000</v>
       </c>
       <c r="E22" s="3">
-        <v>108000</v>
+        <v>107000</v>
       </c>
       <c r="F22" s="3">
         <v>108000</v>
       </c>
       <c r="G22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="H22" s="3">
         <v>106000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>109000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>114000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>115000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>118000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1474,53 +1514,56 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>588000</v>
+      </c>
+      <c r="E23" s="3">
         <v>458000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>346000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>577000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>65000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>427000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>357000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>585000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>639000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>609000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>512000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>738000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>775000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2408000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1530,53 +1573,56 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E24" s="3">
         <v>136000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>53000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>194000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>131000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>30000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>147000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>209000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>140000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>151000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>153000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>171000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>788000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1586,8 +1632,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1642,53 +1691,56 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E26" s="3">
         <v>322000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>293000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>383000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>58000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>296000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>327000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>438000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>430000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>469000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>361000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>585000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>604000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1620000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,53 +1750,56 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E27" s="3">
         <v>322000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>293000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>383000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>58000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>296000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>327000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>438000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>430000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>469000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>361000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>585000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>604000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1620000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,8 +1809,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1810,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1866,8 +1927,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1922,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1978,53 +2045,56 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>19000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2000</v>
       </c>
       <c r="H32" s="3">
         <v>3000</v>
       </c>
       <c r="I32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J32" s="3">
         <v>11000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-34000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>19000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2034,53 +2104,56 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E33" s="3">
         <v>322000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>293000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>383000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>58000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>296000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>327000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>438000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>430000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>469000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>361000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>585000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>604000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1620000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,8 +2163,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2146,53 +2222,56 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E35" s="3">
         <v>322000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>293000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>383000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>58000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>296000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>327000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>438000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>430000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>469000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>361000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>585000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>604000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1620000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,58 +2281,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45018</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44927</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44836</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44745</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44472</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2263,8 +2345,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2285,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2307,47 +2393,48 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1070000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1057000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1070000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1057000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1014000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1155000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1382000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1062000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1231000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1691000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1231000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>797000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2450,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2419,47 +2509,50 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2331000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2312000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2165000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2394000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2240000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2160000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2073000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2109000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2096000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2109000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2122000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2141000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,47 +2568,50 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1776000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1680000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1591000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1820000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1849000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1884000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1851000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1885000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2026000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2222000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2226000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2133000</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,47 +2627,50 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E45" s="3">
         <v>188000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>257000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>228000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>250000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>275000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>283000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>252000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>241000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>206000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>298000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>392000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,47 +2686,50 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5854000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5710000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5525000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5941000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5881000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6097000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6138000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5894000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6219000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6439000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5877000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5463000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2643,8 +2745,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2654,8 +2759,8 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>41000</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
         <v>41000</v>
@@ -2664,20 +2769,20 @@
         <v>41000</v>
       </c>
       <c r="I47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="J47" s="3">
         <v>71000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>76000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>78000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>56000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -2699,47 +2804,50 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2038000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1927000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1960000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1898000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2127000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2145000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2181000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1872000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1832000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1836000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1820000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1700000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2755,47 +2863,50 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18290000</v>
+      </c>
+      <c r="E49" s="3">
         <v>17722000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>17317000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18184000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17735000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18410000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18890000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18461000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18759000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19071000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>19038000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18315000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2811,8 +2922,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2867,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2923,47 +3040,50 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>730000</v>
+      </c>
+      <c r="E52" s="3">
         <v>699000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>615000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>633000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>453000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>419000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>413000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>618000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>511000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8025000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>581000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>544000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3099,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3035,47 +3158,50 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27132000</v>
+      </c>
+      <c r="E54" s="3">
         <v>26257000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25601000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26925000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26443000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27283000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27851000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27077000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27542000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35595000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27316000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26022000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3217,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3113,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3135,47 +3265,48 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2568000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2332000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2254000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2274000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2437000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2602000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2489000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2281000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2354000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1781000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1829000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1745000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3191,41 +3322,44 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1591000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2466000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1588000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1688000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1467000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1566000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>643000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>559000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>799000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3238,8 +3372,8 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3247,47 +3381,50 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E59" s="3">
         <v>236000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>156000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>249000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>272000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>334000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>255000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>383000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>239000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>604000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2097000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2122000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,47 +3440,50 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5988000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6666000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5739000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5946000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5937000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6166000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5481000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5161000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5299000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4210000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3926000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3867000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3359,41 +3499,44 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7153000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6385000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7131000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>7139000</v>
       </c>
       <c r="G61" s="3">
         <v>7139000</v>
       </c>
       <c r="H61" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="I61" s="3">
         <v>7131000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7784000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7791000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7804000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7761000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3415,47 +3558,50 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>510000</v>
+      </c>
+      <c r="E62" s="3">
         <v>483000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>460000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>456000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>447000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>443000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>394000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>463000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>473000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>431000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3369000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3228000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3617,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3527,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3583,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3639,47 +3794,50 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16402000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16204000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15933000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16281000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16265000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16662000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16640000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16184000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16502000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15313000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7295000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7095000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,8 +3853,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3717,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3773,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3829,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3885,8 +4053,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3941,47 +4112,50 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-136000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-163000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-93000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>342000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>429000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>485000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>430000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>25474000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>25153000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4171,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4053,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4109,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4165,47 +4348,50 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10730000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10053000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9668000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10644000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10178000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10621000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11211000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10893000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11040000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20282000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20021000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>18927000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4221,8 +4407,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4277,58 +4466,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45018</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44927</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44836</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44745</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44472</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4338,53 +4530,56 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>420000</v>
+      </c>
+      <c r="E81" s="3">
         <v>322000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>293000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>383000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>58000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>296000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>327000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>438000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>430000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>469000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>361000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>585000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>604000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1620000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,8 +4589,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4416,50 +4614,51 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E83" s="3">
         <v>75000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>94000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>71000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>71000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>83000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>69000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>72000</v>
       </c>
       <c r="L83" s="3">
         <v>72000</v>
       </c>
       <c r="M83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="N83" s="3">
         <v>166000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>152000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>161000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4472,8 +4671,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4528,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4584,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4640,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4696,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4752,50 +4966,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>621000</v>
+      </c>
+      <c r="E89" s="3">
         <v>428000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>793000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>249000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>440000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>287000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>950000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>674000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>742000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>802000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>644000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>736000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>807000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4808,8 +5025,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4830,50 +5050,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-179000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-138000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-59000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-90000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-153000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-223000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-114000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-77000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-55000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-159000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-103000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-76000</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -4886,8 +5107,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4942,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4998,50 +5225,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-90000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-167000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-132000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-56000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-85000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-152000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-265000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-105000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-77000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-41000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-167000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-108000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-73000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5054,8 +5284,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5076,40 +5309,41 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E96" s="3">
         <v>392000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>393000</v>
       </c>
       <c r="F96" s="3">
         <v>393000</v>
       </c>
       <c r="G96" s="3">
-        <v>383000</v>
+        <v>393000</v>
       </c>
       <c r="H96" s="3">
         <v>383000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="I96" s="3">
         <v>383000</v>
       </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="K96" s="3">
+        <v>383000</v>
+      </c>
+      <c r="L96" s="3">
         <v>13788000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5132,8 +5366,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5188,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5244,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5300,50 +5543,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-548000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-310000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-587000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-162000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-490000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-326000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-383000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-726000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8806000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7388000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-63000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-635000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-675000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,50 +5602,53 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-36000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-14000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>20000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-34000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-50000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>20000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-34000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-50000</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,50 +5661,53 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>43000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-141000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-227000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>320000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-169000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8155000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8155000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>434000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,6 +5718,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,88 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44836</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44745</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44472</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,59 +747,62 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3780000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3764000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3839000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3741000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3662000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3899000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4000000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3894000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3666000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3915000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4011000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3852000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3767000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3789000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3804000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11321000</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -809,59 +812,62 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1627000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1530000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1572000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1567000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1584000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1613000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1626000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1646000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1623000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1665000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1786000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1727000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1661000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1637000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1646000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4851000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,59 +877,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2153000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2234000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2267000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2174000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2078000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2286000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2374000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2248000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2043000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2250000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2225000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2125000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2106000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2152000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2158000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6470000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +942,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,59 +969,60 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E12" s="3">
         <v>94000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>91000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>99000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>106000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>97000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>105000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>133000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>78000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>99000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>89000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>103000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>90000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>94000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>253000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,8 +1032,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,59 +1097,62 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E14" s="3">
         <v>97000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>68000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>67000</v>
       </c>
-      <c r="G14" s="3">
-        <v>421000</v>
-      </c>
       <c r="H14" s="3">
+        <v>105000</v>
+      </c>
+      <c r="I14" s="3">
         <v>38000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>568000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>149000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>392000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-6000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-22000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>205000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>63000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-10000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>102000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,47 +1162,50 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E15" s="3">
         <v>141000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>142000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>136000</v>
       </c>
-      <c r="G15" s="3">
-        <v>150000</v>
-      </c>
       <c r="H15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="I15" s="3">
         <v>182000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>141000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>149000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>174000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>153000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>148000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>152000</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1205,8 +1227,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,59 +1251,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3106000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3038000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3079000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3116000</v>
       </c>
-      <c r="G17" s="3">
-        <v>2804000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3097000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3207000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3278000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3226000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2832000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3202000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3331000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3221000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3236000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3026000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3024000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8898000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,59 +1314,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>674000</v>
+      </c>
+      <c r="E18" s="3">
         <v>726000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>760000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>625000</v>
       </c>
-      <c r="G18" s="3">
-        <v>858000</v>
-      </c>
       <c r="H18" s="3">
+        <v>565000</v>
+      </c>
+      <c r="I18" s="3">
         <v>692000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>722000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>668000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>834000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>713000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>680000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>631000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>531000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>763000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>780000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2423000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1379,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,59 +1406,60 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="3">
         <v>10000</v>
       </c>
       <c r="F20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G20" s="3">
         <v>6000</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4000</v>
-      </c>
       <c r="H20" s="3">
+        <v>19000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-19000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-3000</v>
       </c>
       <c r="J20" s="3">
         <v>-3000</v>
       </c>
       <c r="K20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L20" s="3">
         <v>-11000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>34000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>23000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-19000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-15000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1436,59 +1469,62 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>711000</v>
+      </c>
+      <c r="E21" s="3">
         <v>857000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>892000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>755000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1012000</v>
-      </c>
       <c r="H21" s="3">
+        <v>551000</v>
+      </c>
+      <c r="I21" s="3">
         <v>893000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>866000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>820000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1019000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>832000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>818000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>760000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>678000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>890000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>936000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2957000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,13 +1534,16 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>107000</v>
+        <v>109000</v>
       </c>
       <c r="E22" s="3">
         <v>107000</v>
@@ -1513,46 +1552,46 @@
         <v>107000</v>
       </c>
       <c r="G22" s="3">
-        <v>108000</v>
+        <v>107000</v>
       </c>
       <c r="H22" s="3">
         <v>108000</v>
       </c>
       <c r="I22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="J22" s="3">
         <v>106000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>109000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>114000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>115000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>118000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1560,59 +1599,62 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>427000</v>
+      </c>
+      <c r="E23" s="3">
         <v>526000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>588000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>458000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>346000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>577000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>65000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>427000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>357000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>585000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>639000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>609000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>512000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>738000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>775000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2408000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,59 +1664,62 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E24" s="3">
         <v>128000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>168000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>136000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>53000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>194000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>131000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>30000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>147000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>209000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>140000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>151000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>153000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>171000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>788000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1684,8 +1729,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,59 +1794,62 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E26" s="3">
         <v>398000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>420000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>322000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>293000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>383000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>58000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>296000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>327000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>438000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>430000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>469000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>361000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>585000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>604000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1620000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,59 +1859,62 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E27" s="3">
         <v>398000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>420000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>322000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>293000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>383000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>58000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>296000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>327000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>438000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>430000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>469000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>361000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>585000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>604000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1620000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1924,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1989,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2054,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2119,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,59 +2184,62 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-10000</v>
+        <v>-2000</v>
       </c>
       <c r="E32" s="3">
         <v>-10000</v>
       </c>
       <c r="F32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-6000</v>
       </c>
-      <c r="G32" s="3">
-        <v>4000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="I32" s="3">
         <v>19000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>3000</v>
       </c>
       <c r="J32" s="3">
         <v>3000</v>
       </c>
       <c r="K32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L32" s="3">
         <v>11000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-34000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-23000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>19000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>25000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2180,59 +2249,62 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E33" s="3">
         <v>398000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>420000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>322000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>293000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>383000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>58000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>296000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>327000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>438000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>430000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>469000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>361000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>585000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>604000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1620000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2314,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,59 +2379,62 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E35" s="3">
         <v>398000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>420000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>322000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>293000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>383000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>58000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>296000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>327000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>438000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>430000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>469000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>361000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>585000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>604000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1620000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,64 +2444,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44836</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44745</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44472</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2514,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2541,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,53 +2566,54 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1062000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1139000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1070000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1057000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1070000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1057000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1014000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1155000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1382000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1062000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1231000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1691000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1231000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>797000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2629,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2605,53 +2694,56 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2382000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2416000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2331000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2312000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2165000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2394000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2240000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2160000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2073000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2109000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2096000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2109000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2122000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2141000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2667,53 +2759,56 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1666000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1794000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1776000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1680000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1591000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1820000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1849000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1884000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1851000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1885000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2026000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2222000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2226000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2133000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,53 +2824,56 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>177000</v>
+      </c>
+      <c r="E45" s="3">
         <v>176000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>175000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>188000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>257000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>228000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>250000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>275000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>283000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>252000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>241000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>206000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>298000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>392000</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,53 +2889,56 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5697000</v>
+      </c>
+      <c r="E46" s="3">
         <v>6032000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5854000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5710000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5525000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5941000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5881000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6097000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6138000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5894000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6219000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6439000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5877000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5463000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,8 +2954,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2870,8 +2974,8 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
-        <v>41000</v>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I47" s="3">
         <v>41000</v>
@@ -2880,20 +2984,20 @@
         <v>41000</v>
       </c>
       <c r="K47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="L47" s="3">
         <v>71000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>76000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>78000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>56000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -2915,53 +3019,56 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2363000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2092000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2038000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1927000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1960000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1898000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2127000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2145000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2181000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1872000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1832000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1836000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1820000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1700000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,53 +3084,56 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18203000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18157000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18290000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>17722000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17317000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>18184000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17735000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18410000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18890000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18461000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18759000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>19071000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19038000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18315000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3039,8 +3149,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3214,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,53 +3279,56 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>730000</v>
+        <v>576000</v>
       </c>
       <c r="E52" s="3">
         <v>730000</v>
       </c>
       <c r="F52" s="3">
+        <v>730000</v>
+      </c>
+      <c r="G52" s="3">
         <v>699000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>615000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>633000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>453000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>419000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>413000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>618000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>511000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8025000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>581000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>544000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3344,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,53 +3409,56 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27076000</v>
+      </c>
+      <c r="E54" s="3">
         <v>27248000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27132000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26257000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25601000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26925000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26443000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27283000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27851000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27077000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27542000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35595000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27316000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26022000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3474,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3501,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,53 +3526,54 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2414000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2403000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2568000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2332000</v>
       </c>
-      <c r="G57" s="3">
-        <v>2254000</v>
-      </c>
       <c r="H57" s="3">
+        <v>2241000</v>
+      </c>
+      <c r="I57" s="3">
         <v>2274000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2437000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2602000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2489000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2281000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2354000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1781000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1829000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1745000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,47 +3589,50 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1496000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1951000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1591000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2466000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1588000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1688000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1467000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1566000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>643000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>559000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>799000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>32000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3512,8 +3645,8 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3521,53 +3654,56 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E59" s="3">
         <v>168000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>142000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>236000</v>
       </c>
-      <c r="G59" s="3">
-        <v>156000</v>
-      </c>
       <c r="H59" s="3">
+        <v>169000</v>
+      </c>
+      <c r="I59" s="3">
         <v>249000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>272000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>334000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>255000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>383000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>239000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>604000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2097000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2122000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,53 +3719,56 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5945000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6156000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5988000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6666000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5739000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5946000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5937000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6166000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5481000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5161000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5299000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4210000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3926000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3867000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,47 +3784,50 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7178000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7158000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7153000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6385000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7131000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>7139000</v>
       </c>
       <c r="I61" s="3">
         <v>7139000</v>
       </c>
       <c r="J61" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="K61" s="3">
         <v>7131000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7784000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7791000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7804000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7761000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3707,53 +3849,56 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>494000</v>
+      </c>
+      <c r="E62" s="3">
         <v>502000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>510000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>483000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>460000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>456000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>447000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>443000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>394000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>463000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>473000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>431000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3369000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3228000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3769,8 +3914,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3979,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4044,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,53 +4109,56 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16311000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16614000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16402000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16204000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15933000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16281000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16265000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16662000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16640000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16184000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16502000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15313000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7295000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7095000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4174,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4201,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4264,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4329,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4394,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,53 +4459,56 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-136000</v>
+        <v>-204000</v>
       </c>
       <c r="E72" s="3">
         <v>-136000</v>
       </c>
       <c r="F72" s="3">
+        <v>-136000</v>
+      </c>
+      <c r="G72" s="3">
         <v>-163000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-93000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>17000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>342000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>429000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>485000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>430000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>25474000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25153000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4524,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4589,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4654,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,53 +4719,56 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10765000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10634000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10730000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10053000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9668000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10644000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10178000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10621000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11211000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10893000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11040000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20282000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20021000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18927000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4784,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,64 +4849,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44836</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44745</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44472</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,59 +4919,62 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E81" s="3">
         <v>398000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>420000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>322000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>293000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>383000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>58000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>296000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>327000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>438000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>430000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>469000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>361000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>585000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>604000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1620000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4984,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,56 +5011,57 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E83" s="3">
         <v>116000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>75000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>94000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>71000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>69000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>71000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>83000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>69000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>72000</v>
       </c>
       <c r="N83" s="3">
         <v>72000</v>
       </c>
       <c r="O83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="P83" s="3">
         <v>166000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>152000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>161000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4876,8 +5074,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5139,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5204,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5269,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5334,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,56 +5399,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>854000</v>
+      </c>
+      <c r="E89" s="3">
         <v>294000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>621000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>428000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>793000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>249000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>440000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>287000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>950000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>674000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>742000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>802000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>644000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>736000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>807000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5464,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,56 +5491,57 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-98000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-88000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-179000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-138000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-59000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-90000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-153000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-223000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-114000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-77000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-55000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-159000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-103000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-76000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5334,8 +5554,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5619,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,56 +5684,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-104000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-90000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-167000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-132000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-56000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-85000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-152000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-265000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-105000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-77000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-167000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-108000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-73000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5520,8 +5749,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5776,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5553,37 +5786,37 @@
         <v>398000</v>
       </c>
       <c r="E96" s="3">
+        <v>398000</v>
+      </c>
+      <c r="F96" s="3">
         <v>393000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>392000</v>
-      </c>
-      <c r="G96" s="3">
-        <v>393000</v>
       </c>
       <c r="H96" s="3">
         <v>393000</v>
       </c>
       <c r="I96" s="3">
-        <v>383000</v>
+        <v>393000</v>
       </c>
       <c r="J96" s="3">
         <v>383000</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="K96" s="3">
         <v>383000</v>
       </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="M96" s="3">
+        <v>383000</v>
+      </c>
+      <c r="N96" s="3">
         <v>13788000</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5606,8 +5839,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5904,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5969,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,56 +6034,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-869000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-110000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-548000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-310000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-587000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-162000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-490000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-326000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-383000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-726000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8806000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7388000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-63000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-635000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-675000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,56 +6099,59 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E101" s="3">
         <v>12000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-36000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>18000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-14000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>20000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-34000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-50000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>20000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-50000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5916,56 +6164,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-77000</v>
+      </c>
+      <c r="E102" s="3">
         <v>69000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>43000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-141000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-227000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>320000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-169000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8155000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8155000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>434000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>9000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6227,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KVUE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>KVUE</t>
   </si>
@@ -656,91 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E7" s="2">
         <v>46019</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45018</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44927</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44836</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44745</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44472</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -750,62 +751,65 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3909000</v>
+      </c>
+      <c r="E8" s="3">
         <v>3780000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3764000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3839000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3741000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3662000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3899000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4000000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3894000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3666000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3915000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4011000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3852000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3767000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3789000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3804000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11321000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,62 +819,65 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1602000</v>
+      </c>
+      <c r="E9" s="3">
         <v>1627000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1530000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1572000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1567000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1584000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1613000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1626000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1646000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1623000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1665000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1786000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1727000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1661000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1637000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1646000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4851000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -880,62 +887,65 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2307000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2153000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2234000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2267000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2174000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2078000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2286000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2374000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2248000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2043000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2250000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2225000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2125000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2106000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2152000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2158000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6470000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -945,8 +955,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,62 +983,63 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E12" s="3">
         <v>98000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>94000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>91000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>99000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>106000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>97000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>105000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>100000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>133000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>78000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>99000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>89000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>103000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>90000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>94000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>253000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1035,8 +1049,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1100,62 +1117,65 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E14" s="3">
         <v>147000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>97000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>68000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>67000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>105000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>38000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>568000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>149000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>392000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-6000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-22000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>205000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>63000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-10000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>102000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1165,50 +1185,53 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E15" s="3">
         <v>39000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>141000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>142000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>136000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>182000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>141000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>149000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>174000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>153000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>148000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>152000</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1230,8 +1253,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1252,62 +1278,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3064000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3106000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3038000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3079000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3116000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3097000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3207000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3278000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3226000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2832000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3202000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3331000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3221000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3236000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3026000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3024000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8898000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,62 +1344,65 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>845000</v>
+      </c>
+      <c r="E18" s="3">
         <v>674000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>726000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>760000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>625000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>565000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>692000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>722000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>668000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>834000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>713000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>680000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>631000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>531000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>763000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>780000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2423000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1382,8 +1412,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1407,62 +1440,63 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>2000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>10000</v>
       </c>
       <c r="F20" s="3">
         <v>10000</v>
       </c>
       <c r="G20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="H20" s="3">
         <v>6000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>19000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-19000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-3000</v>
       </c>
       <c r="K20" s="3">
         <v>-3000</v>
       </c>
       <c r="L20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-11000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>34000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>23000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-19000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-25000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1472,62 +1506,65 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>988000</v>
+      </c>
+      <c r="E21" s="3">
         <v>711000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>857000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>892000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>755000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>551000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>893000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>866000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>820000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1019000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>832000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>818000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>760000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>678000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>890000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>936000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2957000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,16 +1574,19 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E22" s="3">
         <v>109000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>107000</v>
       </c>
       <c r="F22" s="3">
         <v>107000</v>
@@ -1555,46 +1595,46 @@
         <v>107000</v>
       </c>
       <c r="H22" s="3">
-        <v>108000</v>
+        <v>107000</v>
       </c>
       <c r="I22" s="3">
         <v>108000</v>
       </c>
       <c r="J22" s="3">
+        <v>108000</v>
+      </c>
+      <c r="K22" s="3">
         <v>106000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>109000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>114000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>115000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>118000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1602,62 +1642,65 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E23" s="3">
         <v>427000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>526000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>588000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>458000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>346000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>577000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>65000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>427000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>357000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>585000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>639000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>609000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>512000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>738000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>775000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2408000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1667,62 +1710,65 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E24" s="3">
         <v>97000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>128000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>136000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>53000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>194000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>131000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>30000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>147000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>209000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>140000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>153000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>171000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>788000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1732,8 +1778,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1797,62 +1846,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E26" s="3">
         <v>330000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>398000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>420000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>322000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>293000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>383000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>58000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>296000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>327000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>438000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>430000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>469000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>361000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>585000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>604000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1620000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,62 +1914,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E27" s="3">
         <v>330000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>398000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>420000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>322000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>293000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>383000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>58000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>296000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>327000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>438000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>430000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>469000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>361000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>585000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>604000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1620000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1927,8 +1982,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,8 +2050,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2057,8 +2118,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2122,8 +2186,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2187,62 +2254,65 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-10000</v>
       </c>
       <c r="F32" s="3">
         <v>-10000</v>
       </c>
       <c r="G32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-6000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-19000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>19000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>3000</v>
       </c>
       <c r="K32" s="3">
         <v>3000</v>
       </c>
       <c r="L32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M32" s="3">
         <v>11000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-34000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-23000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>19000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>25000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2252,62 +2322,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E33" s="3">
         <v>330000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>398000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>420000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>322000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>293000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>383000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>58000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>296000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>327000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>438000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>430000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>469000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>361000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>585000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>604000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1620000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2317,8 +2390,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2382,62 +2458,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E35" s="3">
         <v>330000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>398000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>420000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>322000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>293000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>383000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>58000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>296000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>327000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>438000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>430000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>469000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>361000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>585000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>604000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1620000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2447,67 +2526,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46019</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45018</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44927</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44836</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44745</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44472</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2517,8 +2599,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2542,8 +2627,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2567,56 +2653,57 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1075000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1062000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1139000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1070000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1057000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1070000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1057000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1014000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1155000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1382000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1062000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1231000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1691000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>797000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2632,8 +2719,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2697,56 +2787,59 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2501000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2382000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2416000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2331000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2312000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2165000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2394000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2240000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2160000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2073000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2109000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2096000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2109000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2122000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2141000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2762,56 +2855,59 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1674000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1666000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1794000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1776000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1680000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1591000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1820000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1849000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1884000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1851000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1885000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2026000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2222000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2226000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2133000</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2827,56 +2923,59 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E45" s="3">
         <v>177000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>176000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>175000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>188000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>257000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>228000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>250000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>275000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>283000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>252000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>241000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>206000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>298000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>392000</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2892,56 +2991,59 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5795000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5697000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6032000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5854000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5710000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5525000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5941000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5881000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6097000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6138000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5894000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6219000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6439000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5877000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5463000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,8 +3059,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2977,8 +3082,8 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
-        <v>41000</v>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J47" s="3">
         <v>41000</v>
@@ -2987,20 +3092,20 @@
         <v>41000</v>
       </c>
       <c r="L47" s="3">
+        <v>41000</v>
+      </c>
+      <c r="M47" s="3">
         <v>71000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>76000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>78000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>56000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3022,56 +3127,59 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2208000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2363000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2092000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2038000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1927000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1960000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1898000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2127000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2145000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2181000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1872000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1832000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1836000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1820000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1700000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3087,56 +3195,59 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>17916000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18203000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18157000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18290000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17722000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17317000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18184000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17735000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18410000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18890000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18461000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18759000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19071000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19038000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18315000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3263,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3217,8 +3331,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3282,56 +3399,59 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>703000</v>
+      </c>
+      <c r="E52" s="3">
         <v>576000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>730000</v>
       </c>
       <c r="F52" s="3">
         <v>730000</v>
       </c>
       <c r="G52" s="3">
+        <v>730000</v>
+      </c>
+      <c r="H52" s="3">
         <v>699000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>615000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>633000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>453000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>419000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>413000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>618000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>511000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8025000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>581000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>544000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3347,8 +3467,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3412,56 +3535,59 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26854000</v>
+      </c>
+      <c r="E54" s="3">
         <v>27076000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27248000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27132000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26257000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25601000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26925000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26443000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27283000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27851000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27077000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27542000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35595000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27316000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26022000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3477,8 +3603,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3502,8 +3631,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3527,56 +3657,57 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2414000</v>
+        <v>2533000</v>
       </c>
       <c r="E57" s="3">
-        <v>2403000</v>
+        <v>2473000</v>
       </c>
       <c r="F57" s="3">
+        <v>2445000</v>
+      </c>
+      <c r="G57" s="3">
         <v>2568000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2332000</v>
       </c>
-      <c r="H57" s="3">
-        <v>2241000</v>
-      </c>
       <c r="I57" s="3">
+        <v>2254000</v>
+      </c>
+      <c r="J57" s="3">
         <v>2274000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2437000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2602000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2489000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2281000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2354000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1781000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1829000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1745000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3592,50 +3723,53 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1631000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1496000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1951000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1591000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2466000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1588000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1688000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1467000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1566000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>643000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>559000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>799000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>32000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3782,8 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3657,56 +3791,59 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>186000</v>
+        <v>127000</v>
       </c>
       <c r="E59" s="3">
-        <v>168000</v>
+        <v>127000</v>
       </c>
       <c r="F59" s="3">
+        <v>126000</v>
+      </c>
+      <c r="G59" s="3">
         <v>142000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>236000</v>
       </c>
-      <c r="H59" s="3">
-        <v>169000</v>
-      </c>
       <c r="I59" s="3">
+        <v>156000</v>
+      </c>
+      <c r="J59" s="3">
         <v>249000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>272000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>334000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>255000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>383000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>239000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>604000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2097000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2122000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3722,56 +3859,59 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5896000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5945000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6156000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5988000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6666000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5739000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5946000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5937000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6166000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5481000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5161000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5299000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4210000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3926000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3867000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3787,50 +3927,53 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7171000</v>
+      </c>
+      <c r="E61" s="3">
         <v>7178000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7158000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7153000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6385000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7131000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>7139000</v>
       </c>
       <c r="J61" s="3">
         <v>7139000</v>
       </c>
       <c r="K61" s="3">
+        <v>7139000</v>
+      </c>
+      <c r="L61" s="3">
         <v>7131000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7784000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7791000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7804000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7761000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3852,56 +3995,59 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E62" s="3">
         <v>494000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>502000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>510000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>483000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>460000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>456000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>447000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>443000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>394000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>463000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>473000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>431000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3369000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3228000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3917,8 +4063,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3982,8 +4131,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4047,8 +4199,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4112,56 +4267,59 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16246000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16311000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16614000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16402000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16204000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15933000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16281000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16265000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16662000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16640000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16184000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16502000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15313000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7295000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7095000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4335,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4202,8 +4363,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4267,8 +4429,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4332,8 +4497,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4397,8 +4565,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4462,56 +4633,59 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-128000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-204000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-136000</v>
       </c>
       <c r="F72" s="3">
         <v>-136000</v>
       </c>
       <c r="G72" s="3">
+        <v>-136000</v>
+      </c>
+      <c r="H72" s="3">
         <v>-163000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-93000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>17000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>342000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>429000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>485000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>430000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>25474000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25153000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4527,8 +4701,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4592,8 +4769,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4657,8 +4837,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4722,56 +4905,59 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10608000</v>
+      </c>
+      <c r="E76" s="3">
         <v>10765000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10634000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10730000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10053000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9668000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10644000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10178000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10621000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11211000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10893000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11040000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20282000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20021000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>18927000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4787,8 +4973,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4852,67 +5041,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E80" s="2">
         <v>46019</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45018</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44927</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44836</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44745</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44472</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4922,62 +5114,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>474000</v>
+      </c>
+      <c r="E81" s="3">
         <v>330000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>398000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>420000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>322000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>293000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>383000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>58000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>296000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>327000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>438000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>430000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>469000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>361000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>585000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>604000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1620000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4987,8 +5182,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5012,59 +5210,60 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>116000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>75000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>94000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>71000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>69000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>71000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>83000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>69000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>72000</v>
       </c>
       <c r="O83" s="3">
         <v>72000</v>
       </c>
       <c r="P83" s="3">
+        <v>72000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>166000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>152000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>161000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5077,8 +5276,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5142,8 +5344,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5207,8 +5412,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5272,8 +5480,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5337,8 +5548,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5402,59 +5616,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E89" s="3">
         <v>854000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>294000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>621000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>428000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>793000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>249000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>440000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>287000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>950000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>674000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>742000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>802000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>644000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>736000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>807000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5684,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5492,59 +5712,60 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-110000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-98000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-88000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-179000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-138000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-59000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-90000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-153000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-223000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-114000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-77000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-55000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-159000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-103000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-76000</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -5557,8 +5778,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5622,8 +5846,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5687,59 +5914,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-167000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-75000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-104000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-90000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-167000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-132000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-56000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-85000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-152000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-265000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-105000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-77000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-167000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-108000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-73000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5752,8 +5982,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5777,8 +6010,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5789,37 +6023,37 @@
         <v>398000</v>
       </c>
       <c r="F96" s="3">
+        <v>398000</v>
+      </c>
+      <c r="G96" s="3">
         <v>393000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>392000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>393000</v>
       </c>
       <c r="I96" s="3">
         <v>393000</v>
       </c>
       <c r="J96" s="3">
-        <v>383000</v>
+        <v>393000</v>
       </c>
       <c r="K96" s="3">
         <v>383000</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="L96" s="3">
         <v>383000</v>
       </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="N96" s="3">
+        <v>383000</v>
+      </c>
+      <c r="O96" s="3">
         <v>13788000</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5842,8 +6076,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5907,8 +6144,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5972,8 +6212,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6037,59 +6280,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-295000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-869000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-110000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-548000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-310000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-587000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-162000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-490000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-326000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-383000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-726000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8806000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7388000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-635000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-675000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6102,59 +6348,62 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-61000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-36000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>18000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>20000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-34000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-50000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>20000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-34000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-50000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6167,59 +6416,62 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-77000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>69000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>43000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-141000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-227000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>320000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-169000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8155000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8155000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>434000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-41000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>9000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6230,6 +6482,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
